--- a/materialien/Statistik_Kurs_NWW_Beispiele.xlsx
+++ b/materialien/Statistik_Kurs_NWW_Beispiele.xlsx
@@ -1,58 +1,45 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://phtg-my.sharepoint.com/personal/sebastian_ehm_ksk_ch/Documents/Schule/KSK/KI an der Schule/KI Projekte/Statistik-Kurse/Statistik_Kurs_NWW_GitHub_Railway/materialien/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_7A22190A09C97C093A519EA23127DEA334BB8BE5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="Calc"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="276" yWindow="12" windowWidth="22764" windowHeight="11268" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
   </bookViews>
   <sheets>
-    <sheet name="Anleitung" sheetId="1" r:id="rId1"/>
-    <sheet name="Rohdaten Creme" sheetId="2" r:id="rId2"/>
-    <sheet name="Häufigkeiten" sheetId="3" r:id="rId3"/>
-    <sheet name="Kennwerte" sheetId="4" r:id="rId4"/>
-    <sheet name="Signifikanz" sheetId="5" r:id="rId5"/>
-    <sheet name="Eigene Daten" sheetId="6" r:id="rId6"/>
+    <sheet name="Anleitung" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Rohdaten Creme" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Häufigkeiten" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Kennwerte" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Signifikanz" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Eigene Daten" sheetId="6" state="visible" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="81">
   <si>
-    <t>Statistik-Kurs NWW an der KSK – Excel-Beispiele</t>
+    <t xml:space="preserve">Statistik-Kurs NWW an der KSK – Excel-Beispiele</t>
   </si>
   <si>
-    <t>Diese Arbeitsmappe enthält die Creme-Daten aus dem Kurs, nachvollziehbare Kennwerte, Diagramme und eine Vorlage für das eigene Forschungsprojekt.</t>
+    <t xml:space="preserve">Diese Arbeitsmappe enthält die Creme-Daten aus dem Kurs, nachvollziehbare Kennwerte, Diagramme und eine Vorlage für das eigene Forschungsprojekt.</t>
   </si>
   <si>
-    <t>Blatt</t>
+    <t xml:space="preserve">Blatt</t>
   </si>
   <si>
-    <t>Wofür es da ist</t>
+    <t xml:space="preserve">Wofür es da ist</t>
   </si>
   <si>
-    <t>Merksätze
+    <t xml:space="preserve">Merksätze
 • Zahlen von 1 bis 9 sind nicht automatisch metrisch. Bewertungen sind meist ordinal.
 • α = 0,05 ist das Signifikanzniveau; dazu gehört ein Konfidenzniveau von 95 %.
 • p &lt; α bedeutet: Das Ergebnis ist unter H₀ so ungewöhnlich, dass H₀ verworfen wird.
@@ -60,232 +47,232 @@
 • Signifikant bedeutet nicht automatisch wichtig.</t>
   </si>
   <si>
-    <t>Rohdaten Creme</t>
+    <t xml:space="preserve">Rohdaten Creme</t>
   </si>
   <si>
-    <t>20 Einzelbewertungen pro Creme; diese Werte sind ordinal.</t>
+    <t xml:space="preserve">20 Einzelbewertungen pro Creme; diese Werte sind ordinal.</t>
   </si>
   <si>
-    <t>Häufigkeiten</t>
+    <t xml:space="preserve">Häufigkeiten</t>
   </si>
   <si>
-    <t>Zählt jede Bewertung von 1 bis 9 und zeigt die Verteilung.</t>
+    <t xml:space="preserve">Zählt jede Bewertung von 1 bis 9 und zeigt die Verteilung.</t>
   </si>
   <si>
-    <t>Kennwerte</t>
+    <t xml:space="preserve">Kennwerte</t>
   </si>
   <si>
-    <t>Modalwert, Median, Mittelwert, Varianz und Standardabweichung.</t>
+    <t xml:space="preserve">Modalwert, Median, Mittelwert, Varianz und Standardabweichung.</t>
   </si>
   <si>
-    <t>Signifikanz</t>
+    <t xml:space="preserve">Signifikanz</t>
   </si>
   <si>
-    <t>Konkrete p-Werte; unabhängige und gepaarte Daten unterscheiden.</t>
+    <t xml:space="preserve">Konkrete p-Werte; unabhängige und gepaarte Daten unterscheiden.</t>
   </si>
   <si>
-    <t>Eigene Daten</t>
+    <t xml:space="preserve">Eigene Daten</t>
   </si>
   <si>
-    <t>Eigene Messwerte eintragen; Kennwerte berechnen sich automatisch.</t>
+    <t xml:space="preserve">Eigene Messwerte eintragen; Kennwerte berechnen sich automatisch.</t>
   </si>
   <si>
-    <t>Quelle: bereitgestellte Kursunterlagen und Beispieltabellen. Die Testwerte dienen dem Lernen; die Wahl des Tests hängt immer von Datentyp und Versuchsplan ab.</t>
+    <t xml:space="preserve">Quelle: bereitgestellte Kursunterlagen und Beispieltabellen. Die Testwerte dienen dem Lernen; die Wahl des Tests hängt immer von Datentyp und Versuchsplan ab.</t>
   </si>
   <si>
-    <t>Rohdaten: Bewertungen der vier Cremes</t>
+    <t xml:space="preserve">Rohdaten: Bewertungen der vier Cremes</t>
   </si>
   <si>
-    <t>Person</t>
+    <t xml:space="preserve">Person</t>
   </si>
   <si>
-    <t>Creme 1</t>
+    <t xml:space="preserve">Creme 1</t>
   </si>
   <si>
-    <t>Creme 2</t>
+    <t xml:space="preserve">Creme 2</t>
   </si>
   <si>
-    <t>Creme 3</t>
+    <t xml:space="preserve">Creme 3</t>
   </si>
   <si>
-    <t>Creme 4</t>
+    <t xml:space="preserve">Creme 4</t>
   </si>
   <si>
-    <t>Hinweis</t>
+    <t xml:space="preserve">Hinweis</t>
   </si>
   <si>
-    <t>Bewertung 1–9 = ordinal</t>
+    <t xml:space="preserve">Bewertung 1–9 = ordinal</t>
   </si>
   <si>
-    <t>Häufigkeiten und Verteilungen</t>
+    <t xml:space="preserve">Häufigkeiten und Verteilungen</t>
   </si>
   <si>
-    <t>Bewertung</t>
+    <t xml:space="preserve">Bewertung</t>
   </si>
   <si>
-    <t>Höchste Häufigkeit</t>
+    <t xml:space="preserve">Höchste Häufigkeit</t>
   </si>
   <si>
-    <t>Kennwerte der Creme-Bewertungen</t>
+    <t xml:space="preserve">Kennwerte der Creme-Bewertungen</t>
   </si>
   <si>
-    <t>Kennwert</t>
+    <t xml:space="preserve">Kennwert</t>
   </si>
   <si>
-    <t>Creme</t>
+    <t xml:space="preserve">Creme</t>
   </si>
   <si>
-    <t>Mittelwert</t>
+    <t xml:space="preserve">Mittelwert</t>
   </si>
   <si>
-    <t>Standardabweichung</t>
+    <t xml:space="preserve">Standardabweichung</t>
   </si>
   <si>
-    <t>n</t>
+    <t xml:space="preserve">n</t>
   </si>
   <si>
-    <t>Modalwert (MODE.SNGL)</t>
+    <t xml:space="preserve">Modalwert (MODE.SNGL)</t>
   </si>
   <si>
-    <t>Median</t>
+    <t xml:space="preserve">Median</t>
   </si>
   <si>
-    <t>Mittelwert*</t>
+    <t xml:space="preserve">Mittelwert*</t>
   </si>
   <si>
-    <t>Varianz (Stichprobe)</t>
+    <t xml:space="preserve">Varianz (Stichprobe)</t>
   </si>
   <si>
-    <t>Standardabweichung (Stichprobe)</t>
+    <t xml:space="preserve">Standardabweichung (Stichprobe)</t>
   </si>
   <si>
-    <t>Minimum</t>
+    <t xml:space="preserve">Minimum</t>
   </si>
   <si>
-    <t>Maximum</t>
+    <t xml:space="preserve">Maximum</t>
   </si>
   <si>
-    <t>*Die Bewertungen sind ordinal. Der Mittelwert wird hier nur zur Demonstration berechnet; für die inhaltliche Beschreibung sind Modalwert und Median geeigneter. Bei mehreren Modalwerten zeigt MODE.SNGL nur einen davon.</t>
+    <t xml:space="preserve">*Die Bewertungen sind ordinal. Der Mittelwert wird hier nur zur Demonstration berechnet; für die inhaltliche Beschreibung sind Modalwert und Median geeigneter. Bei mehreren Modalwerten zeigt MODE.SNGL nur einen davon.</t>
   </si>
   <si>
-    <t>Signifikanz: Beispiele mit konkreten p-Werten</t>
+    <t xml:space="preserve">Signifikanz: Beispiele mit konkreten p-Werten</t>
   </si>
   <si>
-    <t>Vergleich</t>
+    <t xml:space="preserve">Vergleich</t>
   </si>
   <si>
-    <t>Versuchsplan</t>
+    <t xml:space="preserve">Versuchsplan</t>
   </si>
   <si>
-    <t>Test</t>
+    <t xml:space="preserve">Test</t>
   </si>
   <si>
-    <t>p-Wert</t>
+    <t xml:space="preserve">p-Wert</t>
   </si>
   <si>
-    <t>bei α = 0,05</t>
+    <t xml:space="preserve">bei α = 0,05</t>
   </si>
   <si>
-    <t>Interpretation</t>
+    <t xml:space="preserve">Interpretation</t>
   </si>
   <si>
-    <t>Creme 1 vs. 2</t>
+    <t xml:space="preserve">Creme 1 vs. 2</t>
   </si>
   <si>
-    <t>unabhängige Gruppen</t>
+    <t xml:space="preserve">unabhängige Gruppen</t>
   </si>
   <si>
-    <t>Mann-Whitney-U</t>
+    <t xml:space="preserve">Mann-Whitney-U</t>
   </si>
   <si>
-    <t>nicht signifikant</t>
+    <t xml:space="preserve">nicht signifikant</t>
   </si>
   <si>
-    <t>H₀ nicht verwerfen</t>
+    <t xml:space="preserve">H₀ nicht verwerfen</t>
   </si>
   <si>
-    <t>Creme 1 vs. 3</t>
+    <t xml:space="preserve">Creme 1 vs. 3</t>
   </si>
   <si>
-    <t>Creme 1 vs. 4</t>
+    <t xml:space="preserve">Creme 1 vs. 4</t>
   </si>
   <si>
-    <t>signifikant</t>
+    <t xml:space="preserve">signifikant</t>
   </si>
   <si>
-    <t>H₀ verwerfen</t>
+    <t xml:space="preserve">H₀ verwerfen</t>
   </si>
   <si>
-    <t>Creme 2 vs. 4</t>
+    <t xml:space="preserve">Creme 2 vs. 4</t>
   </si>
   <si>
-    <t>Creme 3 vs. 4</t>
+    <t xml:space="preserve">Creme 3 vs. 4</t>
   </si>
   <si>
-    <t>dieselben Personen</t>
+    <t xml:space="preserve">dieselben Personen</t>
   </si>
   <si>
-    <t>Wilcoxon</t>
+    <t xml:space="preserve">Wilcoxon</t>
   </si>
   <si>
-    <t>α = 0,05 ist das Signifikanzniveau und entspricht einem Konfidenzniveau von 95 %. Ein Konfidenzintervall ist ein berechneter Wertebereich. Der p-Wert ist nicht die Wahrscheinlichkeit, dass H₀ wahr ist. Die p-Werte oben sind Lernbeispiele; ob Gruppen unabhängig oder gepaart sind, hängt vom tatsächlichen Versuchsplan ab.</t>
+    <t xml:space="preserve">α = 0,05 ist das Signifikanzniveau und entspricht einem Konfidenzniveau von 95 %. Ein Konfidenzintervall ist ein berechneter Wertebereich. Der p-Wert ist nicht die Wahrscheinlichkeit, dass H₀ wahr ist. Die p-Werte oben sind Lernbeispiele; ob Gruppen unabhängig oder gepaart sind, hängt vom tatsächlichen Versuchsplan ab.</t>
   </si>
   <si>
-    <t>Vorlage: eigene Forschungsdaten</t>
+    <t xml:space="preserve">Vorlage: eigene Forschungsdaten</t>
   </si>
   <si>
-    <t>ID</t>
+    <t xml:space="preserve">ID</t>
   </si>
   <si>
-    <t>Gruppe / Bedingung A</t>
+    <t xml:space="preserve">Gruppe / Bedingung A</t>
   </si>
   <si>
-    <t>Gruppe / Bedingung B</t>
+    <t xml:space="preserve">Gruppe / Bedingung B</t>
   </si>
   <si>
-    <t>Einheit</t>
+    <t xml:space="preserve">Einheit</t>
   </si>
   <si>
-    <t>Bemerkung</t>
+    <t xml:space="preserve">Bemerkung</t>
   </si>
   <si>
-    <t>A</t>
+    <t xml:space="preserve">A</t>
   </si>
   <si>
-    <t>B</t>
+    <t xml:space="preserve">B</t>
   </si>
   <si>
-    <t>Anzahl Werte</t>
+    <t xml:space="preserve">Anzahl Werte</t>
   </si>
   <si>
-    <t>Modalwert</t>
+    <t xml:space="preserve">Modalwert</t>
   </si>
   <si>
-    <t>häufigster Wert</t>
+    <t xml:space="preserve">häufigster Wert</t>
   </si>
   <si>
-    <t>robuste Mitte</t>
+    <t xml:space="preserve">robuste Mitte</t>
   </si>
   <si>
-    <t>nur metrisch sinnvoll</t>
+    <t xml:space="preserve">nur metrisch sinnvoll</t>
   </si>
   <si>
-    <t>Varianz</t>
+    <t xml:space="preserve">Varianz</t>
   </si>
   <si>
-    <t>mittlere quadrierte Abweichung</t>
+    <t xml:space="preserve">mittlere quadrierte Abweichung</t>
   </si>
   <si>
-    <t>Wurzel der Varianz</t>
+    <t xml:space="preserve">Wurzel der Varianz</t>
   </si>
   <si>
-    <t>Spannweite</t>
+    <t xml:space="preserve">Spannweite</t>
   </si>
   <si>
-    <t>Maximum − Minimum</t>
+    <t xml:space="preserve">Maximum − Minimum</t>
   </si>
   <si>
-    <t>Vor der Auswertung klären:
+    <t xml:space="preserve">Vor der Auswertung klären:
 1. Welche Datenart liegt vor?
 2. Sind A und B unabhängig oder gepaart?
 3. Wie gross ist n?
@@ -296,35 +283,70 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0000"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="General"/>
+    <numFmt numFmtId="166" formatCode="0.00"/>
+    <numFmt numFmtId="167" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="9">
     <font>
       <sz val="11"/>
-      <name val="Carlito"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="10"/>
       <color rgb="FF12354A"/>
       <name val="Aptos"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF12354A"/>
       <name val="Aptos"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
-      <i/>
+      <i val="true"/>
       <sz val="10"/>
       <color rgb="FF12354A"/>
       <name val="Aptos"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="Carlito"/>
+      <b val="true"/>
+      <sz val="18"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="6">
@@ -337,33 +359,37 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF12354A"/>
+        <bgColor rgb="FF333333"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFEAF3F5"/>
+        <bgColor rgb="FFFFF1E7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF13857D"/>
+        <bgColor rgb="FF339966"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF1E7"/>
+        <bgColor rgb="FFEAF3F5"/>
       </patternFill>
     </fill>
   </fills>
   <borders count="13">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
@@ -372,7 +398,7 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left style="thin">
         <color rgb="FFCBD8DE"/>
       </left>
@@ -383,7 +409,7 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right style="thin">
         <color rgb="FFCBD8DE"/>
@@ -394,7 +420,7 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left style="thin">
         <color rgb="FFCBD8DE"/>
       </left>
@@ -403,7 +429,7 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right style="thin">
         <color rgb="FFCBD8DE"/>
@@ -412,7 +438,7 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left style="thin">
         <color rgb="FFCBD8DE"/>
       </left>
@@ -423,7 +449,7 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right style="thin">
         <color rgb="FFCBD8DE"/>
@@ -434,7 +460,7 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top style="thin">
@@ -443,7 +469,7 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
@@ -452,7 +478,7 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left style="thin">
         <color rgb="FFCBD8DE"/>
       </left>
@@ -465,7 +491,7 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top style="thin">
@@ -476,7 +502,7 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right style="thin">
         <color rgb="FFCBD8DE"/>
@@ -490,154 +516,317 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="34">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+  <cellXfs count="36">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="3" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="166" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="166" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+  <cellStyles count="6">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <dxfs count="3">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF13857D"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFEAF3F5"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF12354A"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFF1E7"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF13857D"/>
+      <rgbColor rgb="FFCCCCCC"/>
+      <rgbColor rgb="FF8B8B8B"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFEAF3F5"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FFCBD8DE"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF156082"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFD9D9D9"/>
+      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF12354A"/>
+      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="de-DE"/>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
-  <c:style val="2"/>
   <c:chart>
     <c:title>
       <c:tx>
         <c:rich>
-          <a:bodyPr/>
+          <a:bodyPr rot="0"/>
           <a:lstStyle/>
           <a:p>
+            <a:pPr>
+              <a:defRPr b="1" lang="de-CH" sz="1800" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+                <a:ea typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
             <a:r>
-              <a:rPr lang="de-CH"/>
+              <a:rPr b="1" lang="de-CH" sz="1800" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+                <a:ea typeface="Calibri"/>
+              </a:rPr>
               <a:t>Creme 1: Häufigkeit der Bewertungen</a:t>
             </a:r>
           </a:p>
         </c:rich>
       </c:tx>
       <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout/>
       <c:barChart>
         <c:barDir val="col"/>
         <c:grouping val="clustered"/>
@@ -646,14 +835,59 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:v>Creme 1</c:v>
+            <c:strRef>
+              <c:f>"Creme 1"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Creme 1</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:tx>
-          <c:invertIfNegative val="1"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="156082"/>
+            </a:solidFill>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                    <a:ea typeface="Calibri"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator>; </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
-            <c:numRef>
+            <c:strRef>
               <c:f>Häufigkeiten!$U$4:$U$12</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
+              <c:strCache>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
@@ -682,8 +916,8 @@
                 <c:pt idx="8">
                   <c:v>9</c:v>
                 </c:pt>
-              </c:numCache>
-            </c:numRef>
+              </c:strCache>
+            </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
@@ -721,26 +955,14 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-D5DD-4378-9AAA-877102D7084F}"/>
-            </c:ext>
-          </c:extLst>
         </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="48650112"/>
-        <c:axId val="48672768"/>
+        <c:overlap val="0"/>
+        <c:axId val="78348655"/>
+        <c:axId val="17997067"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="48650112"/>
+        <c:axId val="78348655"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -748,27 +970,51 @@
         <c:axPos val="b"/>
         <c:majorGridlines>
           <c:spPr>
-            <a:ln w="9525">
+            <a:ln w="9360">
               <a:solidFill>
-                <a:srgbClr val="CCCCCC"/>
+                <a:srgbClr val="cccccc"/>
               </a:solidFill>
               <a:prstDash val="dash"/>
+              <a:round/>
             </a:ln>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="48672768"/>
+        <c:spPr>
+          <a:ln w="12600">
+            <a:solidFill>
+              <a:srgbClr val="8b8b8b"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+                <a:ea typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="17997067"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="1"/>
+        <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="48672768"/>
+        <c:axId val="17997067"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="10"/>
@@ -778,68 +1024,113 @@
         <c:axPos val="l"/>
         <c:majorGridlines>
           <c:spPr>
-            <a:ln w="9525">
+            <a:ln w="9360">
               <a:solidFill>
-                <a:srgbClr val="CCCCCC"/>
+                <a:srgbClr val="cccccc"/>
               </a:solidFill>
               <a:prstDash val="dash"/>
+              <a:round/>
             </a:ln>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="48650112"/>
+        <c:spPr>
+          <a:ln w="12600">
+            <a:solidFill>
+              <a:srgbClr val="8b8b8b"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+                <a:ea typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="78348655"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="zero"/>
-    <c:showDLblsOverMax val="1"/>
   </c:chart>
   <c:spPr>
-    <a:ln w="9525">
+    <a:solidFill>
+      <a:srgbClr val="ffffff"/>
+    </a:solidFill>
+    <a:ln w="9360">
       <a:solidFill>
-        <a:srgbClr val="D9D9D9"/>
+        <a:srgbClr val="d9d9d9"/>
       </a:solidFill>
-      <a:prstDash val="solid"/>
+      <a:round/>
     </a:ln>
   </c:spPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.78740157499999996" l="0.7" r="0.7" t="0.78740157499999996" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="de-DE"/>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
-  <c:style val="2"/>
   <c:chart>
     <c:title>
       <c:tx>
         <c:rich>
-          <a:bodyPr/>
+          <a:bodyPr rot="0"/>
           <a:lstStyle/>
           <a:p>
+            <a:pPr>
+              <a:defRPr b="1" lang="de-CH" sz="1800" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+                <a:ea typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
             <a:r>
-              <a:rPr lang="de-CH"/>
+              <a:rPr b="1" lang="de-CH" sz="1800" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+                <a:ea typeface="Calibri"/>
+              </a:rPr>
               <a:t>Creme 2: Häufigkeit der Bewertungen</a:t>
             </a:r>
           </a:p>
         </c:rich>
       </c:tx>
       <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout/>
       <c:barChart>
         <c:barDir val="col"/>
         <c:grouping val="clustered"/>
@@ -848,14 +1139,59 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:v>Creme 2</c:v>
+            <c:strRef>
+              <c:f>"Creme 2"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Creme 2</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:tx>
-          <c:invertIfNegative val="1"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="156082"/>
+            </a:solidFill>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                    <a:ea typeface="Calibri"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator>; </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
-            <c:numRef>
+            <c:strRef>
               <c:f>Häufigkeiten!$W$4:$W$12</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
+              <c:strCache>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
@@ -884,8 +1220,8 @@
                 <c:pt idx="8">
                   <c:v>9</c:v>
                 </c:pt>
-              </c:numCache>
-            </c:numRef>
+              </c:strCache>
+            </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
@@ -923,26 +1259,14 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-1552-40F6-B612-C7AE948072AC}"/>
-            </c:ext>
-          </c:extLst>
         </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="48650112"/>
-        <c:axId val="48672768"/>
+        <c:overlap val="0"/>
+        <c:axId val="54393742"/>
+        <c:axId val="88438114"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="48650112"/>
+        <c:axId val="54393742"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -950,27 +1274,51 @@
         <c:axPos val="b"/>
         <c:majorGridlines>
           <c:spPr>
-            <a:ln w="9525">
+            <a:ln w="9360">
               <a:solidFill>
-                <a:srgbClr val="CCCCCC"/>
+                <a:srgbClr val="cccccc"/>
               </a:solidFill>
               <a:prstDash val="dash"/>
+              <a:round/>
             </a:ln>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="48672768"/>
+        <c:spPr>
+          <a:ln w="12600">
+            <a:solidFill>
+              <a:srgbClr val="8b8b8b"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+                <a:ea typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="88438114"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="1"/>
+        <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="48672768"/>
+        <c:axId val="88438114"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="10"/>
@@ -980,68 +1328,113 @@
         <c:axPos val="l"/>
         <c:majorGridlines>
           <c:spPr>
-            <a:ln w="9525">
+            <a:ln w="9360">
               <a:solidFill>
-                <a:srgbClr val="CCCCCC"/>
+                <a:srgbClr val="cccccc"/>
               </a:solidFill>
               <a:prstDash val="dash"/>
+              <a:round/>
             </a:ln>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="48650112"/>
+        <c:spPr>
+          <a:ln w="12600">
+            <a:solidFill>
+              <a:srgbClr val="8b8b8b"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+                <a:ea typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="54393742"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="zero"/>
-    <c:showDLblsOverMax val="1"/>
   </c:chart>
   <c:spPr>
-    <a:ln w="9525">
+    <a:solidFill>
+      <a:srgbClr val="ffffff"/>
+    </a:solidFill>
+    <a:ln w="9360">
       <a:solidFill>
-        <a:srgbClr val="D9D9D9"/>
+        <a:srgbClr val="d9d9d9"/>
       </a:solidFill>
-      <a:prstDash val="solid"/>
+      <a:round/>
     </a:ln>
   </c:spPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.78740157499999996" l="0.7" r="0.7" t="0.78740157499999996" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="de-DE"/>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
-  <c:style val="2"/>
   <c:chart>
     <c:title>
       <c:tx>
         <c:rich>
-          <a:bodyPr/>
+          <a:bodyPr rot="0"/>
           <a:lstStyle/>
           <a:p>
+            <a:pPr>
+              <a:defRPr b="1" lang="de-CH" sz="1800" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+                <a:ea typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
             <a:r>
-              <a:rPr lang="de-CH"/>
+              <a:rPr b="1" lang="de-CH" sz="1800" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+                <a:ea typeface="Calibri"/>
+              </a:rPr>
               <a:t>Creme 3: Häufigkeit der Bewertungen</a:t>
             </a:r>
           </a:p>
         </c:rich>
       </c:tx>
       <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout/>
       <c:barChart>
         <c:barDir val="col"/>
         <c:grouping val="clustered"/>
@@ -1050,14 +1443,59 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:v>Creme 3</c:v>
+            <c:strRef>
+              <c:f>"Creme 3"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Creme 3</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:tx>
-          <c:invertIfNegative val="1"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="156082"/>
+            </a:solidFill>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                    <a:ea typeface="Calibri"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator>; </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
-            <c:numRef>
+            <c:strRef>
               <c:f>Häufigkeiten!$Y$4:$Y$12</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
+              <c:strCache>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
@@ -1086,8 +1524,8 @@
                 <c:pt idx="8">
                   <c:v>9</c:v>
                 </c:pt>
-              </c:numCache>
-            </c:numRef>
+              </c:strCache>
+            </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
@@ -1125,26 +1563,14 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-7372-4219-A41C-3E048433C675}"/>
-            </c:ext>
-          </c:extLst>
         </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="48650112"/>
-        <c:axId val="48672768"/>
+        <c:overlap val="0"/>
+        <c:axId val="90170432"/>
+        <c:axId val="68292382"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="48650112"/>
+        <c:axId val="90170432"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1152,27 +1578,51 @@
         <c:axPos val="b"/>
         <c:majorGridlines>
           <c:spPr>
-            <a:ln w="9525">
+            <a:ln w="9360">
               <a:solidFill>
-                <a:srgbClr val="CCCCCC"/>
+                <a:srgbClr val="cccccc"/>
               </a:solidFill>
               <a:prstDash val="dash"/>
+              <a:round/>
             </a:ln>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="48672768"/>
+        <c:spPr>
+          <a:ln w="12600">
+            <a:solidFill>
+              <a:srgbClr val="8b8b8b"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+                <a:ea typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="68292382"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="1"/>
+        <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="48672768"/>
+        <c:axId val="68292382"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="10"/>
@@ -1182,68 +1632,113 @@
         <c:axPos val="l"/>
         <c:majorGridlines>
           <c:spPr>
-            <a:ln w="9525">
+            <a:ln w="9360">
               <a:solidFill>
-                <a:srgbClr val="CCCCCC"/>
+                <a:srgbClr val="cccccc"/>
               </a:solidFill>
               <a:prstDash val="dash"/>
+              <a:round/>
             </a:ln>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="48650112"/>
+        <c:spPr>
+          <a:ln w="12600">
+            <a:solidFill>
+              <a:srgbClr val="8b8b8b"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+                <a:ea typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="90170432"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="zero"/>
-    <c:showDLblsOverMax val="1"/>
   </c:chart>
   <c:spPr>
-    <a:ln w="9525">
+    <a:solidFill>
+      <a:srgbClr val="ffffff"/>
+    </a:solidFill>
+    <a:ln w="9360">
       <a:solidFill>
-        <a:srgbClr val="D9D9D9"/>
+        <a:srgbClr val="d9d9d9"/>
       </a:solidFill>
-      <a:prstDash val="solid"/>
+      <a:round/>
     </a:ln>
   </c:spPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.78740157499999996" l="0.7" r="0.7" t="0.78740157499999996" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="de-DE"/>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
-  <c:style val="2"/>
   <c:chart>
     <c:title>
       <c:tx>
         <c:rich>
-          <a:bodyPr/>
+          <a:bodyPr rot="0"/>
           <a:lstStyle/>
           <a:p>
+            <a:pPr>
+              <a:defRPr b="1" lang="de-CH" sz="1800" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+                <a:ea typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
             <a:r>
-              <a:rPr lang="de-CH"/>
+              <a:rPr b="1" lang="de-CH" sz="1800" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+                <a:ea typeface="Calibri"/>
+              </a:rPr>
               <a:t>Creme 4: Häufigkeit der Bewertungen</a:t>
             </a:r>
           </a:p>
         </c:rich>
       </c:tx>
       <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout/>
       <c:barChart>
         <c:barDir val="col"/>
         <c:grouping val="clustered"/>
@@ -1252,14 +1747,59 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:v>Creme 4</c:v>
+            <c:strRef>
+              <c:f>"Creme 4"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Creme 4</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:tx>
-          <c:invertIfNegative val="1"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="156082"/>
+            </a:solidFill>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                    <a:ea typeface="Calibri"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator>; </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
-            <c:numRef>
+            <c:strRef>
               <c:f>Häufigkeiten!$AA$4:$AA$12</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
+              <c:strCache>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
@@ -1288,8 +1828,8 @@
                 <c:pt idx="8">
                   <c:v>9</c:v>
                 </c:pt>
-              </c:numCache>
-            </c:numRef>
+              </c:strCache>
+            </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
@@ -1327,26 +1867,14 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-C452-4904-8ACD-0A8663269AD2}"/>
-            </c:ext>
-          </c:extLst>
         </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="48650112"/>
-        <c:axId val="48672768"/>
+        <c:overlap val="0"/>
+        <c:axId val="31436672"/>
+        <c:axId val="56545694"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="48650112"/>
+        <c:axId val="31436672"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1354,27 +1882,51 @@
         <c:axPos val="b"/>
         <c:majorGridlines>
           <c:spPr>
-            <a:ln w="9525">
+            <a:ln w="9360">
               <a:solidFill>
-                <a:srgbClr val="CCCCCC"/>
+                <a:srgbClr val="cccccc"/>
               </a:solidFill>
               <a:prstDash val="dash"/>
+              <a:round/>
             </a:ln>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="48672768"/>
+        <c:spPr>
+          <a:ln w="12600">
+            <a:solidFill>
+              <a:srgbClr val="8b8b8b"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+                <a:ea typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="56545694"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="1"/>
+        <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="48672768"/>
+        <c:axId val="56545694"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="10"/>
@@ -1384,68 +1936,113 @@
         <c:axPos val="l"/>
         <c:majorGridlines>
           <c:spPr>
-            <a:ln w="9525">
+            <a:ln w="9360">
               <a:solidFill>
-                <a:srgbClr val="CCCCCC"/>
+                <a:srgbClr val="cccccc"/>
               </a:solidFill>
               <a:prstDash val="dash"/>
+              <a:round/>
             </a:ln>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="48650112"/>
+        <c:spPr>
+          <a:ln w="12600">
+            <a:solidFill>
+              <a:srgbClr val="8b8b8b"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+                <a:ea typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="31436672"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="zero"/>
-    <c:showDLblsOverMax val="1"/>
   </c:chart>
   <c:spPr>
-    <a:ln w="9525">
+    <a:solidFill>
+      <a:srgbClr val="ffffff"/>
+    </a:solidFill>
+    <a:ln w="9360">
       <a:solidFill>
-        <a:srgbClr val="D9D9D9"/>
+        <a:srgbClr val="d9d9d9"/>
       </a:solidFill>
-      <a:prstDash val="solid"/>
+      <a:round/>
     </a:ln>
   </c:spPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.78740157499999996" l="0.7" r="0.7" t="0.78740157499999996" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="de-DE"/>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
-  <c:style val="2"/>
   <c:chart>
     <c:title>
       <c:tx>
         <c:rich>
-          <a:bodyPr/>
+          <a:bodyPr rot="0"/>
           <a:lstStyle/>
           <a:p>
+            <a:pPr>
+              <a:defRPr b="1" lang="de-CH" sz="1800" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+                <a:ea typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
             <a:r>
-              <a:rPr lang="de-CH"/>
+              <a:rPr b="1" lang="de-CH" sz="1800" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+                <a:ea typeface="Calibri"/>
+              </a:rPr>
               <a:t>Mittelwerte (nur Demonstration)</a:t>
             </a:r>
           </a:p>
         </c:rich>
       </c:tx>
       <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout/>
       <c:barChart>
         <c:barDir val="col"/>
         <c:grouping val="clustered"/>
@@ -1454,9 +2051,55 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:v>Mittelwert</c:v>
+            <c:strRef>
+              <c:f>"Mittelwert"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Mittelwert</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:tx>
-          <c:invertIfNegative val="1"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="156082"/>
+            </a:solidFill>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                    <a:ea typeface="Calibri"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator>; </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>Kennwerte!$N$4:$N$7</c:f>
@@ -1481,7 +2124,7 @@
             <c:numRef>
               <c:f>Kennwerte!$O$4:$O$7</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>5.35</c:v>
@@ -1498,26 +2141,14 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-37E0-49A2-9683-4D9B367CC97C}"/>
-            </c:ext>
-          </c:extLst>
         </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="48650112"/>
-        <c:axId val="48672768"/>
+        <c:overlap val="0"/>
+        <c:axId val="11063668"/>
+        <c:axId val="70239468"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="48650112"/>
+        <c:axId val="11063668"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1525,27 +2156,51 @@
         <c:axPos val="b"/>
         <c:majorGridlines>
           <c:spPr>
-            <a:ln w="9525">
+            <a:ln w="9360">
               <a:solidFill>
-                <a:srgbClr val="CCCCCC"/>
+                <a:srgbClr val="cccccc"/>
               </a:solidFill>
               <a:prstDash val="dash"/>
+              <a:round/>
             </a:ln>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="48672768"/>
+        <c:spPr>
+          <a:ln w="12600">
+            <a:solidFill>
+              <a:srgbClr val="8b8b8b"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+                <a:ea typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="70239468"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="1"/>
+        <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="48672768"/>
+        <c:axId val="70239468"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="9"/>
@@ -1555,68 +2210,113 @@
         <c:axPos val="l"/>
         <c:majorGridlines>
           <c:spPr>
-            <a:ln w="9525">
+            <a:ln w="9360">
               <a:solidFill>
-                <a:srgbClr val="CCCCCC"/>
+                <a:srgbClr val="cccccc"/>
               </a:solidFill>
               <a:prstDash val="dash"/>
+              <a:round/>
             </a:ln>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="48650112"/>
+        <c:spPr>
+          <a:ln w="12600">
+            <a:solidFill>
+              <a:srgbClr val="8b8b8b"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+                <a:ea typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="11063668"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="zero"/>
-    <c:showDLblsOverMax val="1"/>
   </c:chart>
   <c:spPr>
-    <a:ln w="9525">
+    <a:solidFill>
+      <a:srgbClr val="ffffff"/>
+    </a:solidFill>
+    <a:ln w="9360">
       <a:solidFill>
-        <a:srgbClr val="D9D9D9"/>
+        <a:srgbClr val="d9d9d9"/>
       </a:solidFill>
-      <a:prstDash val="solid"/>
+      <a:round/>
     </a:ln>
   </c:spPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.78740157499999996" l="0.7" r="0.7" t="0.78740157499999996" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="de-DE"/>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
-  <c:style val="2"/>
   <c:chart>
     <c:title>
       <c:tx>
         <c:rich>
-          <a:bodyPr/>
+          <a:bodyPr rot="0"/>
           <a:lstStyle/>
           <a:p>
+            <a:pPr>
+              <a:defRPr b="1" lang="de-CH" sz="1800" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+                <a:ea typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
             <a:r>
-              <a:rPr lang="de-CH"/>
+              <a:rPr b="1" lang="de-CH" sz="1800" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+                <a:ea typeface="Calibri"/>
+              </a:rPr>
               <a:t>Standardabweichungen</a:t>
             </a:r>
           </a:p>
         </c:rich>
       </c:tx>
       <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout/>
       <c:barChart>
         <c:barDir val="col"/>
         <c:grouping val="clustered"/>
@@ -1625,9 +2325,55 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:v>Standardabweichung</c:v>
+            <c:strRef>
+              <c:f>"Standardabweichung"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Standardabweichung</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:tx>
-          <c:invertIfNegative val="1"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="156082"/>
+            </a:solidFill>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                    <a:ea typeface="Calibri"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator>; </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>Kennwerte!$Q$4:$Q$7</c:f>
@@ -1652,43 +2398,31 @@
             <c:numRef>
               <c:f>Kennwerte!$R$4:$R$7</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>2.18306882018965</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>2.9824045403173</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>2.02354561157026</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>0.875093979915421</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-8F8D-4F6E-8B51-963451E20A6C}"/>
-            </c:ext>
-          </c:extLst>
         </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="48650112"/>
-        <c:axId val="48672768"/>
+        <c:overlap val="0"/>
+        <c:axId val="85128648"/>
+        <c:axId val="58045734"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="48650112"/>
+        <c:axId val="85128648"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1696,27 +2430,51 @@
         <c:axPos val="b"/>
         <c:majorGridlines>
           <c:spPr>
-            <a:ln w="9525">
+            <a:ln w="9360">
               <a:solidFill>
-                <a:srgbClr val="CCCCCC"/>
+                <a:srgbClr val="cccccc"/>
               </a:solidFill>
               <a:prstDash val="dash"/>
+              <a:round/>
             </a:ln>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="48672768"/>
+        <c:spPr>
+          <a:ln w="12600">
+            <a:solidFill>
+              <a:srgbClr val="8b8b8b"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+                <a:ea typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="58045734"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="1"/>
+        <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="48672768"/>
+        <c:axId val="58045734"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="4"/>
@@ -1726,46 +2484,73 @@
         <c:axPos val="l"/>
         <c:majorGridlines>
           <c:spPr>
-            <a:ln w="9525">
+            <a:ln w="9360">
               <a:solidFill>
-                <a:srgbClr val="CCCCCC"/>
+                <a:srgbClr val="cccccc"/>
               </a:solidFill>
               <a:prstDash val="dash"/>
+              <a:round/>
             </a:ln>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="48650112"/>
+        <c:spPr>
+          <a:ln w="12600">
+            <a:solidFill>
+              <a:srgbClr val="8b8b8b"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+                <a:ea typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="85128648"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="zero"/>
-    <c:showDLblsOverMax val="1"/>
   </c:chart>
   <c:spPr>
-    <a:ln w="9525">
+    <a:solidFill>
+      <a:srgbClr val="ffffff"/>
+    </a:solidFill>
+    <a:ln w="9360">
       <a:solidFill>
-        <a:srgbClr val="D9D9D9"/>
+        <a:srgbClr val="d9d9d9"/>
       </a:solidFill>
-      <a:prstDash val="solid"/>
+      <a:round/>
     </a:ln>
   </c:spPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.78740157499999996" l="0.7" r="0.7" t="0.78740157499999996" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
@@ -1773,25 +2558,19 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>618840</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>39240</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame macro="">
+    <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="0" name="Chart 1"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
+        <a:off x="4848840" y="514440"/>
+        <a:ext cx="3717720" cy="2391840"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1801,7 +2580,7 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>0</xdr:colOff>
@@ -1809,25 +2588,19 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>618840</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>39240</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame macro="">
+    <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Chart">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000003000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="1" name="Chart 2"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
+        <a:off x="9187200" y="514440"/>
+        <a:ext cx="3717720" cy="2391840"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1837,33 +2610,27 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>40320</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>618840</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>39240</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame macro="">
+    <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="4" name="Chart">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000004000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="2" name="Chart 3"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
+        <a:off x="4848840" y="3078720"/>
+        <a:ext cx="3717720" cy="2227680"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1873,33 +2640,27 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>40320</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>618840</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>39240</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame macro="">
+    <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="5" name="Chart">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000005000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="3" name="Chart 4"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
+        <a:off x="9187200" y="3078720"/>
+        <a:ext cx="3717720" cy="2227680"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1913,8 +2674,8 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
@@ -1922,25 +2683,19 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>618840</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>170640</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame macro="">
+    <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="4" name="Chart 1"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
+        <a:off x="6822360" y="514440"/>
+        <a:ext cx="4337640" cy="2228040"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1950,7 +2705,7 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
@@ -1958,25 +2713,19 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>618840</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>171000</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame macro="">
+    <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Chart">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000003000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="5" name="Chart 2"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
+        <a:off x="6822360" y="2914560"/>
+        <a:ext cx="4337640" cy="2228400"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1990,73 +2739,72 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="CremeRohdaten" displayName="CremeRohdaten" ref="A3:F23" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CremeRohdaten" displayName="CremeRohdaten" ref="A3:F23" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Person"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Creme 1"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Creme 2"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Creme 3"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Creme 4"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Hinweis"/>
+    <tableColumn id="1" name="Person"/>
+    <tableColumn id="2" name="Creme 1"/>
+    <tableColumn id="3" name="Creme 2"/>
+    <tableColumn id="4" name="Creme 3"/>
+    <tableColumn id="5" name="Creme 4"/>
+    <tableColumn id="6" name="Hinweis"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="ChatGPT">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChatGPT">
   <a:themeElements>
     <a:clrScheme name="ChatGPT">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="0e2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="e8e8e8"/>
       </a:lt2>
       <a:accent1>
         <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="e97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="196b24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="0f9ed5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="a02b93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="4ea72e"/>
       </a:accent6>
       <a:hlink>
         <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="96607d"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
-        <a:ea typeface="Calibri Light"/>
-        <a:cs typeface="Calibri Light"/>
+        <a:latin typeface="Calibri Light" pitchFamily="0" charset="1"/>
+        <a:ea typeface="Calibri Light" pitchFamily="0" charset="1"/>
+        <a:cs typeface="Calibri Light" pitchFamily="0" charset="1"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:ea typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:cs typeface="Calibri" pitchFamily="0" charset="1"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="ChatGPT">
+    <a:fmtScheme>
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2067,25 +2815,23 @@
               <a:schemeClr val="phClr">
                 <a:tint val="67000"/>
                 <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="73000"/>
                 <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:tint val="81000"/>
                 <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -2093,44 +2839,33 @@
               <a:schemeClr val="phClr">
                 <a:tint val="94000"/>
                 <a:lumMod val="102000"/>
-                <a:satMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:shade val="100000"/>
                 <a:lumMod val="100000"/>
-                <a:satMod val="110000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="78000"/>
                 <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="12700">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="19050">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="25400">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
@@ -2142,13 +2877,7 @@
           <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000">
-              <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -2158,7 +2887,6 @@
         <a:solidFill>
           <a:schemeClr val="phClr">
             <a:tint val="95000"/>
-            <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:gradFill>
@@ -2168,7 +2896,6 @@
                 <a:tint val="93000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
-                <a:satMod val="150000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
@@ -2176,65 +2903,49 @@
                 <a:tint val="98000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
-                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="63000"/>
-                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:Z60"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.796875" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="13.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="23" customWidth="1"/>
-    <col min="2" max="2" width="48" customWidth="1"/>
-    <col min="3" max="3" width="3" customWidth="1"/>
-    <col min="4" max="9" width="13" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="4" style="1" width="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="27.15" customHeight="1">
-      <c r="A1" s="29" t="s">
+    <row r="1" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="F1" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="G1" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="I1" s="29" t="s">
-        <v>0</v>
-      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
       <c r="J1" s="3"/>
       <c r="K1" s="3"/>
       <c r="L1" s="3"/>
@@ -2253,7 +2964,7 @@
       <c r="Y1" s="3"/>
       <c r="Z1" s="3"/>
     </row>
-    <row r="2" spans="1:26">
+    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -2281,18 +2992,18 @@
       <c r="Y2" s="3"/>
       <c r="Z2" s="3"/>
     </row>
-    <row r="3" spans="1:26" ht="33.6" customHeight="1">
-      <c r="A3" s="30" t="s">
+    <row r="3" customFormat="false" ht="33" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="30"/>
-      <c r="C3" s="30"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="30"/>
-      <c r="H3" s="30"/>
-      <c r="I3" s="30"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
@@ -2311,7 +3022,7 @@
       <c r="Y3" s="3"/>
       <c r="Z3" s="3"/>
     </row>
-    <row r="4" spans="1:26">
+    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -2339,22 +3050,22 @@
       <c r="Y4" s="3"/>
       <c r="Z4" s="3"/>
     </row>
-    <row r="5" spans="1:26">
-      <c r="A5" s="2" t="s">
+    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C5" s="3"/>
-      <c r="D5" s="31" t="s">
+      <c r="D5" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="31"/>
-      <c r="F5" s="31"/>
-      <c r="G5" s="31"/>
-      <c r="H5" s="31"/>
-      <c r="I5" s="31"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6"/>
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
@@ -2373,20 +3084,20 @@
       <c r="Y5" s="3"/>
       <c r="Z5" s="3"/>
     </row>
-    <row r="6" spans="1:26">
-      <c r="A6" s="4" t="s">
+    <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="8" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="3"/>
-      <c r="D6" s="31"/>
-      <c r="E6" s="31"/>
-      <c r="F6" s="31"/>
-      <c r="G6" s="31"/>
-      <c r="H6" s="31"/>
-      <c r="I6" s="31"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6"/>
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
@@ -2405,20 +3116,20 @@
       <c r="Y6" s="3"/>
       <c r="Z6" s="3"/>
     </row>
-    <row r="7" spans="1:26">
-      <c r="A7" s="6" t="s">
+    <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="10" t="s">
         <v>8</v>
       </c>
       <c r="C7" s="3"/>
-      <c r="D7" s="31"/>
-      <c r="E7" s="31"/>
-      <c r="F7" s="31"/>
-      <c r="G7" s="31"/>
-      <c r="H7" s="31"/>
-      <c r="I7" s="31"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
@@ -2437,20 +3148,20 @@
       <c r="Y7" s="3"/>
       <c r="Z7" s="3"/>
     </row>
-    <row r="8" spans="1:26" ht="27.6">
-      <c r="A8" s="6" t="s">
+    <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="10" t="s">
         <v>10</v>
       </c>
       <c r="C8" s="3"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="31"/>
-      <c r="G8" s="31"/>
-      <c r="H8" s="31"/>
-      <c r="I8" s="31"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
@@ -2469,20 +3180,20 @@
       <c r="Y8" s="3"/>
       <c r="Z8" s="3"/>
     </row>
-    <row r="9" spans="1:26" ht="27.6">
-      <c r="A9" s="6" t="s">
+    <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="10" t="s">
         <v>12</v>
       </c>
       <c r="C9" s="3"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="31"/>
-      <c r="G9" s="31"/>
-      <c r="H9" s="31"/>
-      <c r="I9" s="31"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
@@ -2501,20 +3212,20 @@
       <c r="Y9" s="3"/>
       <c r="Z9" s="3"/>
     </row>
-    <row r="10" spans="1:26" ht="27.6">
-      <c r="A10" s="8" t="s">
+    <row r="10" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C10" s="3"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="31"/>
-      <c r="G10" s="31"/>
-      <c r="H10" s="31"/>
-      <c r="I10" s="31"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="6"/>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
@@ -2533,7 +3244,7 @@
       <c r="Y10" s="3"/>
       <c r="Z10" s="3"/>
     </row>
-    <row r="11" spans="1:26">
+    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
@@ -2561,18 +3272,18 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
     </row>
-    <row r="12" spans="1:26">
-      <c r="A12" s="32" t="s">
+    <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="32"/>
-      <c r="C12" s="32"/>
-      <c r="D12" s="32"/>
-      <c r="E12" s="32"/>
-      <c r="F12" s="32"/>
-      <c r="G12" s="32"/>
-      <c r="H12" s="32"/>
-      <c r="I12" s="32"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="13"/>
+      <c r="H12" s="13"/>
+      <c r="I12" s="13"/>
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
@@ -2591,16 +3302,16 @@
       <c r="Y12" s="3"/>
       <c r="Z12" s="3"/>
     </row>
-    <row r="13" spans="1:26">
-      <c r="A13" s="32"/>
-      <c r="B13" s="32"/>
-      <c r="C13" s="32"/>
-      <c r="D13" s="32"/>
-      <c r="E13" s="32"/>
-      <c r="F13" s="32"/>
-      <c r="G13" s="32"/>
-      <c r="H13" s="32"/>
-      <c r="I13" s="32"/>
+    <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="13"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="13"/>
+      <c r="G13" s="13"/>
+      <c r="H13" s="13"/>
+      <c r="I13" s="13"/>
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
@@ -2619,7 +3330,7 @@
       <c r="Y13" s="3"/>
       <c r="Z13" s="3"/>
     </row>
-    <row r="14" spans="1:26">
+    <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -2647,7 +3358,7 @@
       <c r="Y14" s="3"/>
       <c r="Z14" s="3"/>
     </row>
-    <row r="15" spans="1:26">
+    <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -2675,7 +3386,7 @@
       <c r="Y15" s="3"/>
       <c r="Z15" s="3"/>
     </row>
-    <row r="16" spans="1:26">
+    <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
@@ -2703,7 +3414,7 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
     </row>
-    <row r="17" spans="1:26">
+    <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3"/>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
@@ -2731,7 +3442,7 @@
       <c r="Y17" s="3"/>
       <c r="Z17" s="3"/>
     </row>
-    <row r="18" spans="1:26">
+    <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3"/>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -2759,7 +3470,7 @@
       <c r="Y18" s="3"/>
       <c r="Z18" s="3"/>
     </row>
-    <row r="19" spans="1:26">
+    <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="3"/>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
@@ -2787,7 +3498,7 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
     </row>
-    <row r="20" spans="1:26">
+    <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="3"/>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
@@ -2815,7 +3526,7 @@
       <c r="Y20" s="3"/>
       <c r="Z20" s="3"/>
     </row>
-    <row r="21" spans="1:26">
+    <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="3"/>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -2843,7 +3554,7 @@
       <c r="Y21" s="3"/>
       <c r="Z21" s="3"/>
     </row>
-    <row r="22" spans="1:26">
+    <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="3"/>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
@@ -2871,7 +3582,7 @@
       <c r="Y22" s="3"/>
       <c r="Z22" s="3"/>
     </row>
-    <row r="23" spans="1:26">
+    <row r="23" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="3"/>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
@@ -2899,7 +3610,7 @@
       <c r="Y23" s="3"/>
       <c r="Z23" s="3"/>
     </row>
-    <row r="24" spans="1:26">
+    <row r="24" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3"/>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
@@ -2927,7 +3638,7 @@
       <c r="Y24" s="3"/>
       <c r="Z24" s="3"/>
     </row>
-    <row r="25" spans="1:26">
+    <row r="25" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="3"/>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
@@ -2955,7 +3666,7 @@
       <c r="Y25" s="3"/>
       <c r="Z25" s="3"/>
     </row>
-    <row r="26" spans="1:26">
+    <row r="26" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3"/>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
@@ -2983,7 +3694,7 @@
       <c r="Y26" s="3"/>
       <c r="Z26" s="3"/>
     </row>
-    <row r="27" spans="1:26">
+    <row r="27" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="3"/>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
@@ -3011,7 +3722,7 @@
       <c r="Y27" s="3"/>
       <c r="Z27" s="3"/>
     </row>
-    <row r="28" spans="1:26">
+    <row r="28" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="3"/>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
@@ -3039,7 +3750,7 @@
       <c r="Y28" s="3"/>
       <c r="Z28" s="3"/>
     </row>
-    <row r="29" spans="1:26">
+    <row r="29" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="3"/>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
@@ -3067,7 +3778,7 @@
       <c r="Y29" s="3"/>
       <c r="Z29" s="3"/>
     </row>
-    <row r="30" spans="1:26">
+    <row r="30" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="3"/>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
@@ -3095,7 +3806,7 @@
       <c r="Y30" s="3"/>
       <c r="Z30" s="3"/>
     </row>
-    <row r="31" spans="1:26">
+    <row r="31" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3"/>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
@@ -3123,7 +3834,7 @@
       <c r="Y31" s="3"/>
       <c r="Z31" s="3"/>
     </row>
-    <row r="32" spans="1:26">
+    <row r="32" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="3"/>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
@@ -3151,7 +3862,7 @@
       <c r="Y32" s="3"/>
       <c r="Z32" s="3"/>
     </row>
-    <row r="33" spans="1:26">
+    <row r="33" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="3"/>
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
@@ -3179,7 +3890,7 @@
       <c r="Y33" s="3"/>
       <c r="Z33" s="3"/>
     </row>
-    <row r="34" spans="1:26">
+    <row r="34" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="3"/>
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
@@ -3207,7 +3918,7 @@
       <c r="Y34" s="3"/>
       <c r="Z34" s="3"/>
     </row>
-    <row r="35" spans="1:26">
+    <row r="35" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="3"/>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
@@ -3235,7 +3946,7 @@
       <c r="Y35" s="3"/>
       <c r="Z35" s="3"/>
     </row>
-    <row r="36" spans="1:26">
+    <row r="36" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="3"/>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
@@ -3263,7 +3974,7 @@
       <c r="Y36" s="3"/>
       <c r="Z36" s="3"/>
     </row>
-    <row r="37" spans="1:26">
+    <row r="37" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="3"/>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
@@ -3291,7 +4002,7 @@
       <c r="Y37" s="3"/>
       <c r="Z37" s="3"/>
     </row>
-    <row r="38" spans="1:26">
+    <row r="38" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="3"/>
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
@@ -3319,7 +4030,7 @@
       <c r="Y38" s="3"/>
       <c r="Z38" s="3"/>
     </row>
-    <row r="39" spans="1:26">
+    <row r="39" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="3"/>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
@@ -3347,7 +4058,7 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
     </row>
-    <row r="40" spans="1:26">
+    <row r="40" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="3"/>
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
@@ -3375,7 +4086,7 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
     </row>
-    <row r="41" spans="1:26">
+    <row r="41" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="3"/>
       <c r="B41" s="3"/>
       <c r="C41" s="3"/>
@@ -3403,7 +4114,7 @@
       <c r="Y41" s="3"/>
       <c r="Z41" s="3"/>
     </row>
-    <row r="42" spans="1:26">
+    <row r="42" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="3"/>
       <c r="B42" s="3"/>
       <c r="C42" s="3"/>
@@ -3431,7 +4142,7 @@
       <c r="Y42" s="3"/>
       <c r="Z42" s="3"/>
     </row>
-    <row r="43" spans="1:26">
+    <row r="43" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="3"/>
       <c r="B43" s="3"/>
       <c r="C43" s="3"/>
@@ -3459,7 +4170,7 @@
       <c r="Y43" s="3"/>
       <c r="Z43" s="3"/>
     </row>
-    <row r="44" spans="1:26">
+    <row r="44" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="3"/>
       <c r="B44" s="3"/>
       <c r="C44" s="3"/>
@@ -3487,7 +4198,7 @@
       <c r="Y44" s="3"/>
       <c r="Z44" s="3"/>
     </row>
-    <row r="45" spans="1:26">
+    <row r="45" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="3"/>
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
@@ -3515,7 +4226,7 @@
       <c r="Y45" s="3"/>
       <c r="Z45" s="3"/>
     </row>
-    <row r="46" spans="1:26">
+    <row r="46" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="3"/>
       <c r="B46" s="3"/>
       <c r="C46" s="3"/>
@@ -3543,7 +4254,7 @@
       <c r="Y46" s="3"/>
       <c r="Z46" s="3"/>
     </row>
-    <row r="47" spans="1:26">
+    <row r="47" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="3"/>
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
@@ -3571,7 +4282,7 @@
       <c r="Y47" s="3"/>
       <c r="Z47" s="3"/>
     </row>
-    <row r="48" spans="1:26">
+    <row r="48" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="3"/>
       <c r="B48" s="3"/>
       <c r="C48" s="3"/>
@@ -3599,7 +4310,7 @@
       <c r="Y48" s="3"/>
       <c r="Z48" s="3"/>
     </row>
-    <row r="49" spans="1:26">
+    <row r="49" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="3"/>
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
@@ -3627,7 +4338,7 @@
       <c r="Y49" s="3"/>
       <c r="Z49" s="3"/>
     </row>
-    <row r="50" spans="1:26">
+    <row r="50" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="3"/>
       <c r="B50" s="3"/>
       <c r="C50" s="3"/>
@@ -3655,7 +4366,7 @@
       <c r="Y50" s="3"/>
       <c r="Z50" s="3"/>
     </row>
-    <row r="51" spans="1:26">
+    <row r="51" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="3"/>
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
@@ -3683,7 +4394,7 @@
       <c r="Y51" s="3"/>
       <c r="Z51" s="3"/>
     </row>
-    <row r="52" spans="1:26">
+    <row r="52" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="3"/>
       <c r="B52" s="3"/>
       <c r="C52" s="3"/>
@@ -3711,7 +4422,7 @@
       <c r="Y52" s="3"/>
       <c r="Z52" s="3"/>
     </row>
-    <row r="53" spans="1:26">
+    <row r="53" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="3"/>
       <c r="B53" s="3"/>
       <c r="C53" s="3"/>
@@ -3739,7 +4450,7 @@
       <c r="Y53" s="3"/>
       <c r="Z53" s="3"/>
     </row>
-    <row r="54" spans="1:26">
+    <row r="54" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="3"/>
       <c r="B54" s="3"/>
       <c r="C54" s="3"/>
@@ -3767,7 +4478,7 @@
       <c r="Y54" s="3"/>
       <c r="Z54" s="3"/>
     </row>
-    <row r="55" spans="1:26">
+    <row r="55" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="3"/>
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
@@ -3795,7 +4506,7 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
     </row>
-    <row r="56" spans="1:26">
+    <row r="56" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="3"/>
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
@@ -3823,7 +4534,7 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
     </row>
-    <row r="57" spans="1:26">
+    <row r="57" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="3"/>
       <c r="B57" s="3"/>
       <c r="C57" s="3"/>
@@ -3851,7 +4562,7 @@
       <c r="Y57" s="3"/>
       <c r="Z57" s="3"/>
     </row>
-    <row r="58" spans="1:26">
+    <row r="58" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="3"/>
       <c r="B58" s="3"/>
       <c r="C58" s="3"/>
@@ -3879,7 +4590,7 @@
       <c r="Y58" s="3"/>
       <c r="Z58" s="3"/>
     </row>
-    <row r="59" spans="1:26">
+    <row r="59" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="3"/>
       <c r="B59" s="3"/>
       <c r="C59" s="3"/>
@@ -3907,7 +4618,7 @@
       <c r="Y59" s="3"/>
       <c r="Z59" s="3"/>
     </row>
-    <row r="60" spans="1:26">
+    <row r="60" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="3"/>
       <c r="B60" s="3"/>
       <c r="C60" s="3"/>
@@ -3942,39 +4653,38 @@
     <mergeCell ref="D5:I10"/>
     <mergeCell ref="A12:I13"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:Z60"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.796875" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="13.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="5" width="13" customWidth="1"/>
-    <col min="6" max="6" width="30" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="2" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="30"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="27.15" customHeight="1">
-      <c r="A1" s="29" t="s">
+    <row r="1" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="C1" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="D1" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="F1" s="29" t="s">
-        <v>16</v>
-      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
       <c r="G1" s="3"/>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
@@ -3996,7 +4706,7 @@
       <c r="Y1" s="3"/>
       <c r="Z1" s="3"/>
     </row>
-    <row r="2" spans="1:26">
+    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -4024,23 +4734,23 @@
       <c r="Y2" s="3"/>
       <c r="Z2" s="3"/>
     </row>
-    <row r="3" spans="1:26">
-      <c r="A3" s="2" t="s">
+    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="5" t="s">
         <v>22</v>
       </c>
       <c r="G3" s="3"/>
@@ -4064,23 +4774,23 @@
       <c r="Y3" s="3"/>
       <c r="Z3" s="3"/>
     </row>
-    <row r="4" spans="1:26">
-      <c r="A4" s="10">
+    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="11">
+      <c r="B4" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="11">
+      <c r="C4" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="D4" s="11">
+      <c r="D4" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="E4" s="11">
+      <c r="E4" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="F4" s="16" t="s">
         <v>23</v>
       </c>
       <c r="G4" s="3"/>
@@ -4104,23 +4814,23 @@
       <c r="Y4" s="3"/>
       <c r="Z4" s="3"/>
     </row>
-    <row r="5" spans="1:26">
-      <c r="A5" s="13">
+    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="14">
+      <c r="B5" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="14">
+      <c r="C5" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="D5" s="14">
+      <c r="D5" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="E5" s="14">
+      <c r="E5" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="F5" s="15"/>
+      <c r="F5" s="19"/>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
@@ -4142,23 +4852,23 @@
       <c r="Y5" s="3"/>
       <c r="Z5" s="3"/>
     </row>
-    <row r="6" spans="1:26">
-      <c r="A6" s="13">
+    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="14">
+      <c r="B6" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="C6" s="14">
+      <c r="C6" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="D6" s="14">
+      <c r="D6" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="E6" s="14">
+      <c r="E6" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="F6" s="15"/>
+      <c r="F6" s="19"/>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
@@ -4180,23 +4890,23 @@
       <c r="Y6" s="3"/>
       <c r="Z6" s="3"/>
     </row>
-    <row r="7" spans="1:26">
-      <c r="A7" s="13">
+    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="14">
+      <c r="B7" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="C7" s="14">
+      <c r="C7" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="D7" s="14">
+      <c r="D7" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="E7" s="14">
+      <c r="E7" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="F7" s="15"/>
+      <c r="F7" s="19"/>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
@@ -4218,23 +4928,23 @@
       <c r="Y7" s="3"/>
       <c r="Z7" s="3"/>
     </row>
-    <row r="8" spans="1:26">
-      <c r="A8" s="13">
+    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="14">
+      <c r="B8" s="18" t="n">
         <v>7</v>
       </c>
-      <c r="C8" s="14">
+      <c r="C8" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="D8" s="14">
+      <c r="D8" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="E8" s="14">
+      <c r="E8" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="F8" s="15"/>
+      <c r="F8" s="19"/>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
@@ -4256,23 +4966,23 @@
       <c r="Y8" s="3"/>
       <c r="Z8" s="3"/>
     </row>
-    <row r="9" spans="1:26">
-      <c r="A9" s="13">
+    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="14">
+      <c r="B9" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="C9" s="14">
+      <c r="C9" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="D9" s="14">
+      <c r="D9" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="E9" s="14">
+      <c r="E9" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="F9" s="15"/>
+      <c r="F9" s="19"/>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
@@ -4294,23 +5004,23 @@
       <c r="Y9" s="3"/>
       <c r="Z9" s="3"/>
     </row>
-    <row r="10" spans="1:26">
-      <c r="A10" s="13">
+    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="17" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="14">
+      <c r="B10" s="18" t="n">
         <v>9</v>
       </c>
-      <c r="C10" s="14">
+      <c r="C10" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="D10" s="14">
+      <c r="D10" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="E10" s="14">
+      <c r="E10" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="F10" s="15"/>
+      <c r="F10" s="19"/>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
@@ -4332,23 +5042,23 @@
       <c r="Y10" s="3"/>
       <c r="Z10" s="3"/>
     </row>
-    <row r="11" spans="1:26">
-      <c r="A11" s="13">
+    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="14">
+      <c r="B11" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="C11" s="14">
+      <c r="C11" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="D11" s="14">
+      <c r="D11" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="E11" s="14">
+      <c r="E11" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="F11" s="15"/>
+      <c r="F11" s="19"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
@@ -4370,23 +5080,23 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
     </row>
-    <row r="12" spans="1:26">
-      <c r="A12" s="13">
+    <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="B12" s="14">
+      <c r="B12" s="18" t="n">
         <v>7</v>
       </c>
-      <c r="C12" s="14">
+      <c r="C12" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="D12" s="14">
+      <c r="D12" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="E12" s="14">
+      <c r="E12" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="F12" s="15"/>
+      <c r="F12" s="19"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
@@ -4408,23 +5118,23 @@
       <c r="Y12" s="3"/>
       <c r="Z12" s="3"/>
     </row>
-    <row r="13" spans="1:26">
-      <c r="A13" s="13">
+    <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="17" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="14">
+      <c r="B13" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="C13" s="14">
+      <c r="C13" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="D13" s="14">
+      <c r="D13" s="18" t="n">
         <v>7</v>
       </c>
-      <c r="E13" s="14">
+      <c r="E13" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="F13" s="15"/>
+      <c r="F13" s="19"/>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
@@ -4446,23 +5156,23 @@
       <c r="Y13" s="3"/>
       <c r="Z13" s="3"/>
     </row>
-    <row r="14" spans="1:26">
-      <c r="A14" s="13">
+    <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="17" t="n">
         <v>11</v>
       </c>
-      <c r="B14" s="14">
+      <c r="B14" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="C14" s="14">
+      <c r="C14" s="18" t="n">
         <v>7</v>
       </c>
-      <c r="D14" s="14">
+      <c r="D14" s="18" t="n">
         <v>7</v>
       </c>
-      <c r="E14" s="14">
+      <c r="E14" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="F14" s="15"/>
+      <c r="F14" s="19"/>
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
@@ -4484,23 +5194,23 @@
       <c r="Y14" s="3"/>
       <c r="Z14" s="3"/>
     </row>
-    <row r="15" spans="1:26">
-      <c r="A15" s="13">
+    <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="17" t="n">
         <v>12</v>
       </c>
-      <c r="B15" s="14">
+      <c r="B15" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="C15" s="14">
+      <c r="C15" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="D15" s="14">
+      <c r="D15" s="18" t="n">
         <v>7</v>
       </c>
-      <c r="E15" s="14">
+      <c r="E15" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="F15" s="15"/>
+      <c r="F15" s="19"/>
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
@@ -4522,23 +5232,23 @@
       <c r="Y15" s="3"/>
       <c r="Z15" s="3"/>
     </row>
-    <row r="16" spans="1:26">
-      <c r="A16" s="13">
+    <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="17" t="n">
         <v>13</v>
       </c>
-      <c r="B16" s="14">
+      <c r="B16" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="C16" s="14">
+      <c r="C16" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="D16" s="14">
+      <c r="D16" s="18" t="n">
         <v>7</v>
       </c>
-      <c r="E16" s="14">
+      <c r="E16" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="F16" s="15"/>
+      <c r="F16" s="19"/>
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
@@ -4560,23 +5270,23 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
     </row>
-    <row r="17" spans="1:26">
-      <c r="A17" s="13">
+    <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="17" t="n">
         <v>14</v>
       </c>
-      <c r="B17" s="14">
+      <c r="B17" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="C17" s="14">
+      <c r="C17" s="18" t="n">
         <v>9</v>
       </c>
-      <c r="D17" s="14">
+      <c r="D17" s="18" t="n">
         <v>7</v>
       </c>
-      <c r="E17" s="14">
+      <c r="E17" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="F17" s="15"/>
+      <c r="F17" s="19"/>
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
@@ -4598,23 +5308,23 @@
       <c r="Y17" s="3"/>
       <c r="Z17" s="3"/>
     </row>
-    <row r="18" spans="1:26">
-      <c r="A18" s="13">
+    <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="17" t="n">
         <v>15</v>
       </c>
-      <c r="B18" s="14">
+      <c r="B18" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="C18" s="14">
+      <c r="C18" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="D18" s="14">
+      <c r="D18" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="E18" s="14">
+      <c r="E18" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="F18" s="15"/>
+      <c r="F18" s="19"/>
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
@@ -4636,23 +5346,23 @@
       <c r="Y18" s="3"/>
       <c r="Z18" s="3"/>
     </row>
-    <row r="19" spans="1:26">
-      <c r="A19" s="13">
+    <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="17" t="n">
         <v>16</v>
       </c>
-      <c r="B19" s="14">
+      <c r="B19" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="C19" s="14">
+      <c r="C19" s="18" t="n">
         <v>7</v>
       </c>
-      <c r="D19" s="14">
+      <c r="D19" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="E19" s="14">
+      <c r="E19" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="F19" s="15"/>
+      <c r="F19" s="19"/>
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
       <c r="I19" s="3"/>
@@ -4674,23 +5384,23 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
     </row>
-    <row r="20" spans="1:26">
-      <c r="A20" s="13">
+    <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="17" t="n">
         <v>17</v>
       </c>
-      <c r="B20" s="14">
+      <c r="B20" s="18" t="n">
         <v>7</v>
       </c>
-      <c r="C20" s="14">
+      <c r="C20" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="D20" s="14">
+      <c r="D20" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="E20" s="14">
+      <c r="E20" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="F20" s="15"/>
+      <c r="F20" s="19"/>
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
@@ -4712,23 +5422,23 @@
       <c r="Y20" s="3"/>
       <c r="Z20" s="3"/>
     </row>
-    <row r="21" spans="1:26">
-      <c r="A21" s="13">
+    <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="17" t="n">
         <v>18</v>
       </c>
-      <c r="B21" s="14">
+      <c r="B21" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="C21" s="14">
+      <c r="C21" s="18" t="n">
         <v>7</v>
       </c>
-      <c r="D21" s="14">
+      <c r="D21" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="E21" s="14">
+      <c r="E21" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="F21" s="15"/>
+      <c r="F21" s="19"/>
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
@@ -4750,23 +5460,23 @@
       <c r="Y21" s="3"/>
       <c r="Z21" s="3"/>
     </row>
-    <row r="22" spans="1:26">
-      <c r="A22" s="13">
+    <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="17" t="n">
         <v>19</v>
       </c>
-      <c r="B22" s="14">
+      <c r="B22" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="C22" s="14">
+      <c r="C22" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="D22" s="14">
+      <c r="D22" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="E22" s="14">
+      <c r="E22" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="F22" s="15"/>
+      <c r="F22" s="19"/>
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
@@ -4788,23 +5498,23 @@
       <c r="Y22" s="3"/>
       <c r="Z22" s="3"/>
     </row>
-    <row r="23" spans="1:26">
-      <c r="A23" s="16">
+    <row r="23" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="20" t="n">
         <v>20</v>
       </c>
-      <c r="B23" s="17">
+      <c r="B23" s="21" t="n">
         <v>6</v>
       </c>
-      <c r="C23" s="17">
+      <c r="C23" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="17">
+      <c r="D23" s="21" t="n">
         <v>9</v>
       </c>
-      <c r="E23" s="17">
+      <c r="E23" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="F23" s="18"/>
+      <c r="F23" s="22"/>
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
@@ -4826,7 +5536,7 @@
       <c r="Y23" s="3"/>
       <c r="Z23" s="3"/>
     </row>
-    <row r="24" spans="1:26">
+    <row r="24" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3"/>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
@@ -4854,7 +5564,7 @@
       <c r="Y24" s="3"/>
       <c r="Z24" s="3"/>
     </row>
-    <row r="25" spans="1:26">
+    <row r="25" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="3"/>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
@@ -4882,7 +5592,7 @@
       <c r="Y25" s="3"/>
       <c r="Z25" s="3"/>
     </row>
-    <row r="26" spans="1:26">
+    <row r="26" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3"/>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
@@ -4910,7 +5620,7 @@
       <c r="Y26" s="3"/>
       <c r="Z26" s="3"/>
     </row>
-    <row r="27" spans="1:26">
+    <row r="27" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="3"/>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
@@ -4938,7 +5648,7 @@
       <c r="Y27" s="3"/>
       <c r="Z27" s="3"/>
     </row>
-    <row r="28" spans="1:26">
+    <row r="28" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="3"/>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
@@ -4966,7 +5676,7 @@
       <c r="Y28" s="3"/>
       <c r="Z28" s="3"/>
     </row>
-    <row r="29" spans="1:26">
+    <row r="29" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="3"/>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
@@ -4994,7 +5704,7 @@
       <c r="Y29" s="3"/>
       <c r="Z29" s="3"/>
     </row>
-    <row r="30" spans="1:26">
+    <row r="30" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="3"/>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
@@ -5022,7 +5732,7 @@
       <c r="Y30" s="3"/>
       <c r="Z30" s="3"/>
     </row>
-    <row r="31" spans="1:26">
+    <row r="31" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3"/>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
@@ -5050,7 +5760,7 @@
       <c r="Y31" s="3"/>
       <c r="Z31" s="3"/>
     </row>
-    <row r="32" spans="1:26">
+    <row r="32" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="3"/>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
@@ -5078,7 +5788,7 @@
       <c r="Y32" s="3"/>
       <c r="Z32" s="3"/>
     </row>
-    <row r="33" spans="1:26">
+    <row r="33" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="3"/>
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
@@ -5106,7 +5816,7 @@
       <c r="Y33" s="3"/>
       <c r="Z33" s="3"/>
     </row>
-    <row r="34" spans="1:26">
+    <row r="34" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="3"/>
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
@@ -5134,7 +5844,7 @@
       <c r="Y34" s="3"/>
       <c r="Z34" s="3"/>
     </row>
-    <row r="35" spans="1:26">
+    <row r="35" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="3"/>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
@@ -5162,7 +5872,7 @@
       <c r="Y35" s="3"/>
       <c r="Z35" s="3"/>
     </row>
-    <row r="36" spans="1:26">
+    <row r="36" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="3"/>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
@@ -5190,7 +5900,7 @@
       <c r="Y36" s="3"/>
       <c r="Z36" s="3"/>
     </row>
-    <row r="37" spans="1:26">
+    <row r="37" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="3"/>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
@@ -5218,7 +5928,7 @@
       <c r="Y37" s="3"/>
       <c r="Z37" s="3"/>
     </row>
-    <row r="38" spans="1:26">
+    <row r="38" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="3"/>
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
@@ -5246,7 +5956,7 @@
       <c r="Y38" s="3"/>
       <c r="Z38" s="3"/>
     </row>
-    <row r="39" spans="1:26">
+    <row r="39" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="3"/>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
@@ -5274,7 +5984,7 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
     </row>
-    <row r="40" spans="1:26">
+    <row r="40" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="3"/>
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
@@ -5302,7 +6012,7 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
     </row>
-    <row r="41" spans="1:26">
+    <row r="41" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="3"/>
       <c r="B41" s="3"/>
       <c r="C41" s="3"/>
@@ -5330,7 +6040,7 @@
       <c r="Y41" s="3"/>
       <c r="Z41" s="3"/>
     </row>
-    <row r="42" spans="1:26">
+    <row r="42" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="3"/>
       <c r="B42" s="3"/>
       <c r="C42" s="3"/>
@@ -5358,7 +6068,7 @@
       <c r="Y42" s="3"/>
       <c r="Z42" s="3"/>
     </row>
-    <row r="43" spans="1:26">
+    <row r="43" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="3"/>
       <c r="B43" s="3"/>
       <c r="C43" s="3"/>
@@ -5386,7 +6096,7 @@
       <c r="Y43" s="3"/>
       <c r="Z43" s="3"/>
     </row>
-    <row r="44" spans="1:26">
+    <row r="44" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="3"/>
       <c r="B44" s="3"/>
       <c r="C44" s="3"/>
@@ -5414,7 +6124,7 @@
       <c r="Y44" s="3"/>
       <c r="Z44" s="3"/>
     </row>
-    <row r="45" spans="1:26">
+    <row r="45" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="3"/>
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
@@ -5442,7 +6152,7 @@
       <c r="Y45" s="3"/>
       <c r="Z45" s="3"/>
     </row>
-    <row r="46" spans="1:26">
+    <row r="46" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="3"/>
       <c r="B46" s="3"/>
       <c r="C46" s="3"/>
@@ -5470,7 +6180,7 @@
       <c r="Y46" s="3"/>
       <c r="Z46" s="3"/>
     </row>
-    <row r="47" spans="1:26">
+    <row r="47" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="3"/>
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
@@ -5498,7 +6208,7 @@
       <c r="Y47" s="3"/>
       <c r="Z47" s="3"/>
     </row>
-    <row r="48" spans="1:26">
+    <row r="48" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="3"/>
       <c r="B48" s="3"/>
       <c r="C48" s="3"/>
@@ -5526,7 +6236,7 @@
       <c r="Y48" s="3"/>
       <c r="Z48" s="3"/>
     </row>
-    <row r="49" spans="1:26">
+    <row r="49" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="3"/>
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
@@ -5554,7 +6264,7 @@
       <c r="Y49" s="3"/>
       <c r="Z49" s="3"/>
     </row>
-    <row r="50" spans="1:26">
+    <row r="50" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="3"/>
       <c r="B50" s="3"/>
       <c r="C50" s="3"/>
@@ -5582,7 +6292,7 @@
       <c r="Y50" s="3"/>
       <c r="Z50" s="3"/>
     </row>
-    <row r="51" spans="1:26">
+    <row r="51" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="3"/>
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
@@ -5610,7 +6320,7 @@
       <c r="Y51" s="3"/>
       <c r="Z51" s="3"/>
     </row>
-    <row r="52" spans="1:26">
+    <row r="52" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="3"/>
       <c r="B52" s="3"/>
       <c r="C52" s="3"/>
@@ -5638,7 +6348,7 @@
       <c r="Y52" s="3"/>
       <c r="Z52" s="3"/>
     </row>
-    <row r="53" spans="1:26">
+    <row r="53" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="3"/>
       <c r="B53" s="3"/>
       <c r="C53" s="3"/>
@@ -5666,7 +6376,7 @@
       <c r="Y53" s="3"/>
       <c r="Z53" s="3"/>
     </row>
-    <row r="54" spans="1:26">
+    <row r="54" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="3"/>
       <c r="B54" s="3"/>
       <c r="C54" s="3"/>
@@ -5694,7 +6404,7 @@
       <c r="Y54" s="3"/>
       <c r="Z54" s="3"/>
     </row>
-    <row r="55" spans="1:26">
+    <row r="55" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="3"/>
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
@@ -5722,7 +6432,7 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
     </row>
-    <row r="56" spans="1:26">
+    <row r="56" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="3"/>
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
@@ -5750,7 +6460,7 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
     </row>
-    <row r="57" spans="1:26">
+    <row r="57" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="3"/>
       <c r="B57" s="3"/>
       <c r="C57" s="3"/>
@@ -5778,7 +6488,7 @@
       <c r="Y57" s="3"/>
       <c r="Z57" s="3"/>
     </row>
-    <row r="58" spans="1:26">
+    <row r="58" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="3"/>
       <c r="B58" s="3"/>
       <c r="C58" s="3"/>
@@ -5806,7 +6516,7 @@
       <c r="Y58" s="3"/>
       <c r="Z58" s="3"/>
     </row>
-    <row r="59" spans="1:26">
+    <row r="59" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="3"/>
       <c r="B59" s="3"/>
       <c r="C59" s="3"/>
@@ -5834,7 +6544,7 @@
       <c r="Y59" s="3"/>
       <c r="Z59" s="3"/>
     </row>
-    <row r="60" spans="1:26">
+    <row r="60" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="3"/>
       <c r="B60" s="3"/>
       <c r="C60" s="3"/>
@@ -5866,79 +6576,52 @@
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <tableParts>
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:AB60"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.796875" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="13.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="5" width="12" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="1" width="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="27.15" customHeight="1">
-      <c r="A1" s="29" t="s">
+    <row r="1" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="C1" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="D1" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="E1" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="F1" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="G1" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="H1" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="I1" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="J1" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="K1" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="L1" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="M1" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="N1" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="O1" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="P1" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q1" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="R1" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="S1" s="29" t="s">
-        <v>24</v>
-      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
       <c r="T1" s="3"/>
       <c r="U1" s="3"/>
       <c r="V1" s="3"/>
@@ -5947,7 +6630,7 @@
       <c r="Y1" s="3"/>
       <c r="Z1" s="3"/>
     </row>
-    <row r="2" spans="1:28">
+    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -5975,20 +6658,20 @@
       <c r="Y2" s="3"/>
       <c r="Z2" s="3"/>
     </row>
-    <row r="3" spans="1:28">
-      <c r="A3" s="2" t="s">
+    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="5" t="s">
         <v>21</v>
       </c>
       <c r="F3" s="3"/>
@@ -6024,31 +6707,31 @@
       <c r="Z3" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="AA3" t="s">
+      <c r="AA3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AB3" t="s">
+      <c r="AB3" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:28">
-      <c r="A4" s="4">
+    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="19">
-        <f>COUNTIF('Rohdaten Creme'!$B$4:$B$23,$A4)</f>
+      <c r="B4" s="23" t="n">
+        <f aca="false">COUNTIF('Rohdaten Creme'!$B$4:$B$23,$A4)</f>
         <v>1</v>
       </c>
-      <c r="C4" s="19">
-        <f>COUNTIF('Rohdaten Creme'!$C$4:$C$23,$A4)</f>
+      <c r="C4" s="23" t="n">
+        <f aca="false">COUNTIF('Rohdaten Creme'!$C$4:$C$23,$A4)</f>
         <v>4</v>
       </c>
-      <c r="D4" s="19">
-        <f>COUNTIF('Rohdaten Creme'!$D$4:$D$23,$A4)</f>
+      <c r="D4" s="23" t="n">
+        <f aca="false">COUNTIF('Rohdaten Creme'!$D$4:$D$23,$A4)</f>
         <v>0</v>
       </c>
-      <c r="E4" s="5">
-        <f>COUNTIF('Rohdaten Creme'!$E$4:$E$23,$A4)</f>
+      <c r="E4" s="8" t="n">
+        <f aca="false">COUNTIF('Rohdaten Creme'!$E$4:$E$23,$A4)</f>
         <v>3</v>
       </c>
       <c r="F4" s="3"/>
@@ -6066,57 +6749,57 @@
       <c r="R4" s="3"/>
       <c r="S4" s="3"/>
       <c r="T4" s="3"/>
-      <c r="U4" s="3">
-        <f t="shared" ref="U4:U12" si="0">A4</f>
+      <c r="U4" s="3" t="n">
+        <f aca="false">A4</f>
         <v>1</v>
       </c>
-      <c r="V4" s="3">
-        <f t="shared" ref="V4:V12" si="1">B4</f>
+      <c r="V4" s="3" t="n">
+        <f aca="false">B4</f>
         <v>1</v>
       </c>
-      <c r="W4" s="3">
-        <f t="shared" ref="W4:W12" si="2">A4</f>
+      <c r="W4" s="3" t="n">
+        <f aca="false">A4</f>
         <v>1</v>
       </c>
-      <c r="X4" s="3">
-        <f t="shared" ref="X4:X12" si="3">C4</f>
+      <c r="X4" s="3" t="n">
+        <f aca="false">C4</f>
         <v>4</v>
       </c>
-      <c r="Y4" s="3">
-        <f t="shared" ref="Y4:Y12" si="4">A4</f>
+      <c r="Y4" s="3" t="n">
+        <f aca="false">A4</f>
         <v>1</v>
       </c>
-      <c r="Z4" s="3">
-        <f t="shared" ref="Z4:Z12" si="5">D4</f>
+      <c r="Z4" s="3" t="n">
+        <f aca="false">D4</f>
         <v>0</v>
       </c>
-      <c r="AA4">
-        <f t="shared" ref="AA4:AA12" si="6">A4</f>
+      <c r="AA4" s="1" t="n">
+        <f aca="false">A4</f>
         <v>1</v>
       </c>
-      <c r="AB4">
-        <f t="shared" ref="AB4:AB12" si="7">E4</f>
+      <c r="AB4" s="1" t="n">
+        <f aca="false">E4</f>
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:28">
-      <c r="A5" s="6">
+    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="1">
-        <f>COUNTIF('Rohdaten Creme'!$B$4:$B$23,$A5)</f>
+      <c r="B5" s="24" t="n">
+        <f aca="false">COUNTIF('Rohdaten Creme'!$B$4:$B$23,$A5)</f>
         <v>2</v>
       </c>
-      <c r="C5" s="1">
-        <f>COUNTIF('Rohdaten Creme'!$C$4:$C$23,$A5)</f>
+      <c r="C5" s="24" t="n">
+        <f aca="false">COUNTIF('Rohdaten Creme'!$C$4:$C$23,$A5)</f>
         <v>4</v>
       </c>
-      <c r="D5" s="1">
-        <f>COUNTIF('Rohdaten Creme'!$D$4:$D$23,$A5)</f>
+      <c r="D5" s="24" t="n">
+        <f aca="false">COUNTIF('Rohdaten Creme'!$D$4:$D$23,$A5)</f>
         <v>1</v>
       </c>
-      <c r="E5" s="7">
-        <f>COUNTIF('Rohdaten Creme'!$E$4:$E$23,$A5)</f>
+      <c r="E5" s="10" t="n">
+        <f aca="false">COUNTIF('Rohdaten Creme'!$E$4:$E$23,$A5)</f>
         <v>9</v>
       </c>
       <c r="F5" s="3"/>
@@ -6134,57 +6817,57 @@
       <c r="R5" s="3"/>
       <c r="S5" s="3"/>
       <c r="T5" s="3"/>
-      <c r="U5" s="3">
-        <f t="shared" si="0"/>
+      <c r="U5" s="3" t="n">
+        <f aca="false">A5</f>
         <v>2</v>
       </c>
-      <c r="V5" s="3">
-        <f t="shared" si="1"/>
+      <c r="V5" s="3" t="n">
+        <f aca="false">B5</f>
         <v>2</v>
       </c>
-      <c r="W5" s="3">
-        <f t="shared" si="2"/>
+      <c r="W5" s="3" t="n">
+        <f aca="false">A5</f>
         <v>2</v>
       </c>
-      <c r="X5" s="3">
-        <f t="shared" si="3"/>
+      <c r="X5" s="3" t="n">
+        <f aca="false">C5</f>
         <v>4</v>
       </c>
-      <c r="Y5" s="3">
-        <f t="shared" si="4"/>
+      <c r="Y5" s="3" t="n">
+        <f aca="false">A5</f>
         <v>2</v>
       </c>
-      <c r="Z5" s="3">
-        <f t="shared" si="5"/>
+      <c r="Z5" s="3" t="n">
+        <f aca="false">D5</f>
         <v>1</v>
       </c>
-      <c r="AA5">
-        <f t="shared" si="6"/>
+      <c r="AA5" s="1" t="n">
+        <f aca="false">A5</f>
         <v>2</v>
       </c>
-      <c r="AB5">
-        <f t="shared" si="7"/>
+      <c r="AB5" s="1" t="n">
+        <f aca="false">E5</f>
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:28">
-      <c r="A6" s="6">
+    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="1">
-        <f>COUNTIF('Rohdaten Creme'!$B$4:$B$23,$A6)</f>
+      <c r="B6" s="24" t="n">
+        <f aca="false">COUNTIF('Rohdaten Creme'!$B$4:$B$23,$A6)</f>
         <v>2</v>
       </c>
-      <c r="C6" s="1">
-        <f>COUNTIF('Rohdaten Creme'!$C$4:$C$23,$A6)</f>
+      <c r="C6" s="24" t="n">
+        <f aca="false">COUNTIF('Rohdaten Creme'!$C$4:$C$23,$A6)</f>
         <v>2</v>
       </c>
-      <c r="D6" s="1">
-        <f>COUNTIF('Rohdaten Creme'!$D$4:$D$23,$A6)</f>
+      <c r="D6" s="24" t="n">
+        <f aca="false">COUNTIF('Rohdaten Creme'!$D$4:$D$23,$A6)</f>
         <v>2</v>
       </c>
-      <c r="E6" s="7">
-        <f>COUNTIF('Rohdaten Creme'!$E$4:$E$23,$A6)</f>
+      <c r="E6" s="10" t="n">
+        <f aca="false">COUNTIF('Rohdaten Creme'!$E$4:$E$23,$A6)</f>
         <v>6</v>
       </c>
       <c r="F6" s="3"/>
@@ -6202,57 +6885,57 @@
       <c r="R6" s="3"/>
       <c r="S6" s="3"/>
       <c r="T6" s="3"/>
-      <c r="U6" s="3">
-        <f t="shared" si="0"/>
+      <c r="U6" s="3" t="n">
+        <f aca="false">A6</f>
         <v>3</v>
       </c>
-      <c r="V6" s="3">
-        <f t="shared" si="1"/>
+      <c r="V6" s="3" t="n">
+        <f aca="false">B6</f>
         <v>2</v>
       </c>
-      <c r="W6" s="3">
-        <f t="shared" si="2"/>
+      <c r="W6" s="3" t="n">
+        <f aca="false">A6</f>
         <v>3</v>
       </c>
-      <c r="X6" s="3">
-        <f t="shared" si="3"/>
+      <c r="X6" s="3" t="n">
+        <f aca="false">C6</f>
         <v>2</v>
       </c>
-      <c r="Y6" s="3">
-        <f t="shared" si="4"/>
+      <c r="Y6" s="3" t="n">
+        <f aca="false">A6</f>
         <v>3</v>
       </c>
-      <c r="Z6" s="3">
-        <f t="shared" si="5"/>
+      <c r="Z6" s="3" t="n">
+        <f aca="false">D6</f>
         <v>2</v>
       </c>
-      <c r="AA6">
-        <f t="shared" si="6"/>
+      <c r="AA6" s="1" t="n">
+        <f aca="false">A6</f>
         <v>3</v>
       </c>
-      <c r="AB6">
-        <f t="shared" si="7"/>
+      <c r="AB6" s="1" t="n">
+        <f aca="false">E6</f>
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:28">
-      <c r="A7" s="6">
+    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="1">
-        <f>COUNTIF('Rohdaten Creme'!$B$4:$B$23,$A7)</f>
+      <c r="B7" s="24" t="n">
+        <f aca="false">COUNTIF('Rohdaten Creme'!$B$4:$B$23,$A7)</f>
         <v>0</v>
       </c>
-      <c r="C7" s="1">
-        <f>COUNTIF('Rohdaten Creme'!$C$4:$C$23,$A7)</f>
+      <c r="C7" s="24" t="n">
+        <f aca="false">COUNTIF('Rohdaten Creme'!$C$4:$C$23,$A7)</f>
         <v>1</v>
       </c>
-      <c r="D7" s="1">
-        <f>COUNTIF('Rohdaten Creme'!$D$4:$D$23,$A7)</f>
+      <c r="D7" s="24" t="n">
+        <f aca="false">COUNTIF('Rohdaten Creme'!$D$4:$D$23,$A7)</f>
         <v>2</v>
       </c>
-      <c r="E7" s="7">
-        <f>COUNTIF('Rohdaten Creme'!$E$4:$E$23,$A7)</f>
+      <c r="E7" s="10" t="n">
+        <f aca="false">COUNTIF('Rohdaten Creme'!$E$4:$E$23,$A7)</f>
         <v>2</v>
       </c>
       <c r="F7" s="3"/>
@@ -6270,57 +6953,57 @@
       <c r="R7" s="3"/>
       <c r="S7" s="3"/>
       <c r="T7" s="3"/>
-      <c r="U7" s="3">
-        <f t="shared" si="0"/>
+      <c r="U7" s="3" t="n">
+        <f aca="false">A7</f>
         <v>4</v>
       </c>
-      <c r="V7" s="3">
-        <f t="shared" si="1"/>
+      <c r="V7" s="3" t="n">
+        <f aca="false">B7</f>
         <v>0</v>
       </c>
-      <c r="W7" s="3">
-        <f t="shared" si="2"/>
+      <c r="W7" s="3" t="n">
+        <f aca="false">A7</f>
         <v>4</v>
       </c>
-      <c r="X7" s="3">
-        <f t="shared" si="3"/>
+      <c r="X7" s="3" t="n">
+        <f aca="false">C7</f>
         <v>1</v>
       </c>
-      <c r="Y7" s="3">
-        <f t="shared" si="4"/>
+      <c r="Y7" s="3" t="n">
+        <f aca="false">A7</f>
         <v>4</v>
       </c>
-      <c r="Z7" s="3">
-        <f t="shared" si="5"/>
+      <c r="Z7" s="3" t="n">
+        <f aca="false">D7</f>
         <v>2</v>
       </c>
-      <c r="AA7">
-        <f t="shared" si="6"/>
+      <c r="AA7" s="1" t="n">
+        <f aca="false">A7</f>
         <v>4</v>
       </c>
-      <c r="AB7">
-        <f t="shared" si="7"/>
+      <c r="AB7" s="1" t="n">
+        <f aca="false">E7</f>
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:28">
-      <c r="A8" s="6">
+    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="1">
-        <f>COUNTIF('Rohdaten Creme'!$B$4:$B$23,$A8)</f>
+      <c r="B8" s="24" t="n">
+        <f aca="false">COUNTIF('Rohdaten Creme'!$B$4:$B$23,$A8)</f>
         <v>4</v>
       </c>
-      <c r="C8" s="1">
-        <f>COUNTIF('Rohdaten Creme'!$C$4:$C$23,$A8)</f>
+      <c r="C8" s="24" t="n">
+        <f aca="false">COUNTIF('Rohdaten Creme'!$C$4:$C$23,$A8)</f>
         <v>0</v>
       </c>
-      <c r="D8" s="1">
-        <f>COUNTIF('Rohdaten Creme'!$D$4:$D$23,$A8)</f>
+      <c r="D8" s="24" t="n">
+        <f aca="false">COUNTIF('Rohdaten Creme'!$D$4:$D$23,$A8)</f>
         <v>2</v>
       </c>
-      <c r="E8" s="7">
-        <f>COUNTIF('Rohdaten Creme'!$E$4:$E$23,$A8)</f>
+      <c r="E8" s="10" t="n">
+        <f aca="false">COUNTIF('Rohdaten Creme'!$E$4:$E$23,$A8)</f>
         <v>0</v>
       </c>
       <c r="F8" s="3"/>
@@ -6338,57 +7021,57 @@
       <c r="R8" s="3"/>
       <c r="S8" s="3"/>
       <c r="T8" s="3"/>
-      <c r="U8" s="3">
-        <f t="shared" si="0"/>
+      <c r="U8" s="3" t="n">
+        <f aca="false">A8</f>
         <v>5</v>
       </c>
-      <c r="V8" s="3">
-        <f t="shared" si="1"/>
+      <c r="V8" s="3" t="n">
+        <f aca="false">B8</f>
         <v>4</v>
       </c>
-      <c r="W8" s="3">
-        <f t="shared" si="2"/>
+      <c r="W8" s="3" t="n">
+        <f aca="false">A8</f>
         <v>5</v>
       </c>
-      <c r="X8" s="3">
-        <f t="shared" si="3"/>
+      <c r="X8" s="3" t="n">
+        <f aca="false">C8</f>
         <v>0</v>
       </c>
-      <c r="Y8" s="3">
-        <f t="shared" si="4"/>
+      <c r="Y8" s="3" t="n">
+        <f aca="false">A8</f>
         <v>5</v>
       </c>
-      <c r="Z8" s="3">
-        <f t="shared" si="5"/>
+      <c r="Z8" s="3" t="n">
+        <f aca="false">D8</f>
         <v>2</v>
       </c>
-      <c r="AA8">
-        <f t="shared" si="6"/>
+      <c r="AA8" s="1" t="n">
+        <f aca="false">A8</f>
         <v>5</v>
       </c>
-      <c r="AB8">
-        <f t="shared" si="7"/>
+      <c r="AB8" s="1" t="n">
+        <f aca="false">E8</f>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:28">
-      <c r="A9" s="6">
+    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="1">
-        <f>COUNTIF('Rohdaten Creme'!$B$4:$B$23,$A9)</f>
+      <c r="B9" s="24" t="n">
+        <f aca="false">COUNTIF('Rohdaten Creme'!$B$4:$B$23,$A9)</f>
         <v>5</v>
       </c>
-      <c r="C9" s="1">
-        <f>COUNTIF('Rohdaten Creme'!$C$4:$C$23,$A9)</f>
+      <c r="C9" s="24" t="n">
+        <f aca="false">COUNTIF('Rohdaten Creme'!$C$4:$C$23,$A9)</f>
         <v>1</v>
       </c>
-      <c r="D9" s="1">
-        <f>COUNTIF('Rohdaten Creme'!$D$4:$D$23,$A9)</f>
+      <c r="D9" s="24" t="n">
+        <f aca="false">COUNTIF('Rohdaten Creme'!$D$4:$D$23,$A9)</f>
         <v>2</v>
       </c>
-      <c r="E9" s="7">
-        <f>COUNTIF('Rohdaten Creme'!$E$4:$E$23,$A9)</f>
+      <c r="E9" s="10" t="n">
+        <f aca="false">COUNTIF('Rohdaten Creme'!$E$4:$E$23,$A9)</f>
         <v>0</v>
       </c>
       <c r="F9" s="3"/>
@@ -6406,57 +7089,57 @@
       <c r="R9" s="3"/>
       <c r="S9" s="3"/>
       <c r="T9" s="3"/>
-      <c r="U9" s="3">
-        <f t="shared" si="0"/>
+      <c r="U9" s="3" t="n">
+        <f aca="false">A9</f>
         <v>6</v>
       </c>
-      <c r="V9" s="3">
-        <f t="shared" si="1"/>
+      <c r="V9" s="3" t="n">
+        <f aca="false">B9</f>
         <v>5</v>
       </c>
-      <c r="W9" s="3">
-        <f t="shared" si="2"/>
+      <c r="W9" s="3" t="n">
+        <f aca="false">A9</f>
         <v>6</v>
       </c>
-      <c r="X9" s="3">
-        <f t="shared" si="3"/>
+      <c r="X9" s="3" t="n">
+        <f aca="false">C9</f>
         <v>1</v>
       </c>
-      <c r="Y9" s="3">
-        <f t="shared" si="4"/>
+      <c r="Y9" s="3" t="n">
+        <f aca="false">A9</f>
         <v>6</v>
       </c>
-      <c r="Z9" s="3">
-        <f t="shared" si="5"/>
+      <c r="Z9" s="3" t="n">
+        <f aca="false">D9</f>
         <v>2</v>
       </c>
-      <c r="AA9">
-        <f t="shared" si="6"/>
+      <c r="AA9" s="1" t="n">
+        <f aca="false">A9</f>
         <v>6</v>
       </c>
-      <c r="AB9">
-        <f t="shared" si="7"/>
+      <c r="AB9" s="1" t="n">
+        <f aca="false">E9</f>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:28">
-      <c r="A10" s="6">
+    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="1">
-        <f>COUNTIF('Rohdaten Creme'!$B$4:$B$23,$A10)</f>
+      <c r="B10" s="24" t="n">
+        <f aca="false">COUNTIF('Rohdaten Creme'!$B$4:$B$23,$A10)</f>
         <v>3</v>
       </c>
-      <c r="C10" s="1">
-        <f>COUNTIF('Rohdaten Creme'!$C$4:$C$23,$A10)</f>
+      <c r="C10" s="24" t="n">
+        <f aca="false">COUNTIF('Rohdaten Creme'!$C$4:$C$23,$A10)</f>
         <v>3</v>
       </c>
-      <c r="D10" s="1">
-        <f>COUNTIF('Rohdaten Creme'!$D$4:$D$23,$A10)</f>
+      <c r="D10" s="24" t="n">
+        <f aca="false">COUNTIF('Rohdaten Creme'!$D$4:$D$23,$A10)</f>
         <v>5</v>
       </c>
-      <c r="E10" s="7">
-        <f>COUNTIF('Rohdaten Creme'!$E$4:$E$23,$A10)</f>
+      <c r="E10" s="10" t="n">
+        <f aca="false">COUNTIF('Rohdaten Creme'!$E$4:$E$23,$A10)</f>
         <v>0</v>
       </c>
       <c r="F10" s="3"/>
@@ -6474,57 +7157,57 @@
       <c r="R10" s="3"/>
       <c r="S10" s="3"/>
       <c r="T10" s="3"/>
-      <c r="U10" s="3">
-        <f t="shared" si="0"/>
+      <c r="U10" s="3" t="n">
+        <f aca="false">A10</f>
         <v>7</v>
       </c>
-      <c r="V10" s="3">
-        <f t="shared" si="1"/>
+      <c r="V10" s="3" t="n">
+        <f aca="false">B10</f>
         <v>3</v>
       </c>
-      <c r="W10" s="3">
-        <f t="shared" si="2"/>
+      <c r="W10" s="3" t="n">
+        <f aca="false">A10</f>
         <v>7</v>
       </c>
-      <c r="X10" s="3">
-        <f t="shared" si="3"/>
+      <c r="X10" s="3" t="n">
+        <f aca="false">C10</f>
         <v>3</v>
       </c>
-      <c r="Y10" s="3">
-        <f t="shared" si="4"/>
+      <c r="Y10" s="3" t="n">
+        <f aca="false">A10</f>
         <v>7</v>
       </c>
-      <c r="Z10" s="3">
-        <f t="shared" si="5"/>
+      <c r="Z10" s="3" t="n">
+        <f aca="false">D10</f>
         <v>5</v>
       </c>
-      <c r="AA10">
-        <f t="shared" si="6"/>
+      <c r="AA10" s="1" t="n">
+        <f aca="false">A10</f>
         <v>7</v>
       </c>
-      <c r="AB10">
-        <f t="shared" si="7"/>
+      <c r="AB10" s="1" t="n">
+        <f aca="false">E10</f>
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:28">
-      <c r="A11" s="6">
+    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="1">
-        <f>COUNTIF('Rohdaten Creme'!$B$4:$B$23,$A11)</f>
+      <c r="B11" s="24" t="n">
+        <f aca="false">COUNTIF('Rohdaten Creme'!$B$4:$B$23,$A11)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="1">
-        <f>COUNTIF('Rohdaten Creme'!$C$4:$C$23,$A11)</f>
+      <c r="C11" s="24" t="n">
+        <f aca="false">COUNTIF('Rohdaten Creme'!$C$4:$C$23,$A11)</f>
         <v>4</v>
       </c>
-      <c r="D11" s="1">
-        <f>COUNTIF('Rohdaten Creme'!$D$4:$D$23,$A11)</f>
+      <c r="D11" s="24" t="n">
+        <f aca="false">COUNTIF('Rohdaten Creme'!$D$4:$D$23,$A11)</f>
         <v>5</v>
       </c>
-      <c r="E11" s="7">
-        <f>COUNTIF('Rohdaten Creme'!$E$4:$E$23,$A11)</f>
+      <c r="E11" s="10" t="n">
+        <f aca="false">COUNTIF('Rohdaten Creme'!$E$4:$E$23,$A11)</f>
         <v>0</v>
       </c>
       <c r="F11" s="3"/>
@@ -6542,57 +7225,57 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-      <c r="U11" s="3">
-        <f t="shared" si="0"/>
+      <c r="U11" s="3" t="n">
+        <f aca="false">A11</f>
         <v>8</v>
       </c>
-      <c r="V11" s="3">
-        <f t="shared" si="1"/>
+      <c r="V11" s="3" t="n">
+        <f aca="false">B11</f>
         <v>2</v>
       </c>
-      <c r="W11" s="3">
-        <f t="shared" si="2"/>
+      <c r="W11" s="3" t="n">
+        <f aca="false">A11</f>
         <v>8</v>
       </c>
-      <c r="X11" s="3">
-        <f t="shared" si="3"/>
+      <c r="X11" s="3" t="n">
+        <f aca="false">C11</f>
         <v>4</v>
       </c>
-      <c r="Y11" s="3">
-        <f t="shared" si="4"/>
+      <c r="Y11" s="3" t="n">
+        <f aca="false">A11</f>
         <v>8</v>
       </c>
-      <c r="Z11" s="3">
-        <f t="shared" si="5"/>
+      <c r="Z11" s="3" t="n">
+        <f aca="false">D11</f>
         <v>5</v>
       </c>
-      <c r="AA11">
-        <f t="shared" si="6"/>
+      <c r="AA11" s="1" t="n">
+        <f aca="false">A11</f>
         <v>8</v>
       </c>
-      <c r="AB11">
-        <f t="shared" si="7"/>
+      <c r="AB11" s="1" t="n">
+        <f aca="false">E11</f>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:28">
-      <c r="A12" s="8">
+    <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="B12" s="20">
-        <f>COUNTIF('Rohdaten Creme'!$B$4:$B$23,$A12)</f>
+      <c r="B12" s="25" t="n">
+        <f aca="false">COUNTIF('Rohdaten Creme'!$B$4:$B$23,$A12)</f>
         <v>1</v>
       </c>
-      <c r="C12" s="20">
-        <f>COUNTIF('Rohdaten Creme'!$C$4:$C$23,$A12)</f>
+      <c r="C12" s="25" t="n">
+        <f aca="false">COUNTIF('Rohdaten Creme'!$C$4:$C$23,$A12)</f>
         <v>1</v>
       </c>
-      <c r="D12" s="20">
-        <f>COUNTIF('Rohdaten Creme'!$D$4:$D$23,$A12)</f>
+      <c r="D12" s="25" t="n">
+        <f aca="false">COUNTIF('Rohdaten Creme'!$D$4:$D$23,$A12)</f>
         <v>1</v>
       </c>
-      <c r="E12" s="9">
-        <f>COUNTIF('Rohdaten Creme'!$E$4:$E$23,$A12)</f>
+      <c r="E12" s="12" t="n">
+        <f aca="false">COUNTIF('Rohdaten Creme'!$E$4:$E$23,$A12)</f>
         <v>0</v>
       </c>
       <c r="F12" s="3"/>
@@ -6610,40 +7293,40 @@
       <c r="R12" s="3"/>
       <c r="S12" s="3"/>
       <c r="T12" s="3"/>
-      <c r="U12" s="3">
-        <f t="shared" si="0"/>
+      <c r="U12" s="3" t="n">
+        <f aca="false">A12</f>
         <v>9</v>
       </c>
-      <c r="V12" s="3">
-        <f t="shared" si="1"/>
+      <c r="V12" s="3" t="n">
+        <f aca="false">B12</f>
         <v>1</v>
       </c>
-      <c r="W12" s="3">
-        <f t="shared" si="2"/>
+      <c r="W12" s="3" t="n">
+        <f aca="false">A12</f>
         <v>9</v>
       </c>
-      <c r="X12" s="3">
-        <f t="shared" si="3"/>
+      <c r="X12" s="3" t="n">
+        <f aca="false">C12</f>
         <v>1</v>
       </c>
-      <c r="Y12" s="3">
-        <f t="shared" si="4"/>
+      <c r="Y12" s="3" t="n">
+        <f aca="false">A12</f>
         <v>9</v>
       </c>
-      <c r="Z12" s="3">
-        <f t="shared" si="5"/>
+      <c r="Z12" s="3" t="n">
+        <f aca="false">D12</f>
         <v>1</v>
       </c>
-      <c r="AA12">
-        <f t="shared" si="6"/>
+      <c r="AA12" s="1" t="n">
+        <f aca="false">A12</f>
         <v>9</v>
       </c>
-      <c r="AB12">
-        <f t="shared" si="7"/>
+      <c r="AB12" s="1" t="n">
+        <f aca="false">E12</f>
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:28">
+    <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -6671,18 +7354,18 @@
       <c r="Y13" s="3"/>
       <c r="Z13" s="3"/>
     </row>
-    <row r="14" spans="1:28">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2" t="s">
+    <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="5"/>
+      <c r="B14" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E14" s="5" t="s">
         <v>21</v>
       </c>
       <c r="F14" s="3"/>
@@ -6707,24 +7390,24 @@
       <c r="Y14" s="3"/>
       <c r="Z14" s="3"/>
     </row>
-    <row r="15" spans="1:28" ht="27.6">
-      <c r="A15" s="21" t="s">
+    <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="B15" s="22">
-        <f>MAX(B4:B12)</f>
+      <c r="B15" s="27" t="n">
+        <f aca="false">MAX(B4:B12)</f>
         <v>5</v>
       </c>
-      <c r="C15" s="22">
-        <f>MAX(C4:C12)</f>
+      <c r="C15" s="27" t="n">
+        <f aca="false">MAX(C4:C12)</f>
         <v>4</v>
       </c>
-      <c r="D15" s="22">
-        <f>MAX(D4:D12)</f>
+      <c r="D15" s="27" t="n">
+        <f aca="false">MAX(D4:D12)</f>
         <v>5</v>
       </c>
-      <c r="E15" s="23">
-        <f>MAX(E4:E12)</f>
+      <c r="E15" s="28" t="n">
+        <f aca="false">MAX(E4:E12)</f>
         <v>9</v>
       </c>
       <c r="F15" s="3"/>
@@ -6749,7 +7432,7 @@
       <c r="Y15" s="3"/>
       <c r="Z15" s="3"/>
     </row>
-    <row r="16" spans="1:28">
+    <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
@@ -6777,7 +7460,7 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
     </row>
-    <row r="17" spans="1:26">
+    <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3"/>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
@@ -6805,7 +7488,7 @@
       <c r="Y17" s="3"/>
       <c r="Z17" s="3"/>
     </row>
-    <row r="18" spans="1:26">
+    <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3"/>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -6833,7 +7516,7 @@
       <c r="Y18" s="3"/>
       <c r="Z18" s="3"/>
     </row>
-    <row r="19" spans="1:26">
+    <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="3"/>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
@@ -6861,7 +7544,7 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
     </row>
-    <row r="20" spans="1:26">
+    <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="3"/>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
@@ -6889,7 +7572,7 @@
       <c r="Y20" s="3"/>
       <c r="Z20" s="3"/>
     </row>
-    <row r="21" spans="1:26">
+    <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="3"/>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -6917,7 +7600,7 @@
       <c r="Y21" s="3"/>
       <c r="Z21" s="3"/>
     </row>
-    <row r="22" spans="1:26">
+    <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="3"/>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
@@ -6945,7 +7628,7 @@
       <c r="Y22" s="3"/>
       <c r="Z22" s="3"/>
     </row>
-    <row r="23" spans="1:26">
+    <row r="23" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="3"/>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
@@ -6973,7 +7656,7 @@
       <c r="Y23" s="3"/>
       <c r="Z23" s="3"/>
     </row>
-    <row r="24" spans="1:26">
+    <row r="24" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3"/>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
@@ -7001,7 +7684,7 @@
       <c r="Y24" s="3"/>
       <c r="Z24" s="3"/>
     </row>
-    <row r="25" spans="1:26">
+    <row r="25" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="3"/>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
@@ -7029,7 +7712,7 @@
       <c r="Y25" s="3"/>
       <c r="Z25" s="3"/>
     </row>
-    <row r="26" spans="1:26">
+    <row r="26" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3"/>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
@@ -7057,7 +7740,7 @@
       <c r="Y26" s="3"/>
       <c r="Z26" s="3"/>
     </row>
-    <row r="27" spans="1:26">
+    <row r="27" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="3"/>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
@@ -7085,7 +7768,7 @@
       <c r="Y27" s="3"/>
       <c r="Z27" s="3"/>
     </row>
-    <row r="28" spans="1:26">
+    <row r="28" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="3"/>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
@@ -7113,7 +7796,7 @@
       <c r="Y28" s="3"/>
       <c r="Z28" s="3"/>
     </row>
-    <row r="29" spans="1:26">
+    <row r="29" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="3"/>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
@@ -7141,7 +7824,7 @@
       <c r="Y29" s="3"/>
       <c r="Z29" s="3"/>
     </row>
-    <row r="30" spans="1:26">
+    <row r="30" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="3"/>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
@@ -7169,7 +7852,7 @@
       <c r="Y30" s="3"/>
       <c r="Z30" s="3"/>
     </row>
-    <row r="31" spans="1:26">
+    <row r="31" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3"/>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
@@ -7197,7 +7880,7 @@
       <c r="Y31" s="3"/>
       <c r="Z31" s="3"/>
     </row>
-    <row r="32" spans="1:26">
+    <row r="32" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="3"/>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
@@ -7225,7 +7908,7 @@
       <c r="Y32" s="3"/>
       <c r="Z32" s="3"/>
     </row>
-    <row r="33" spans="1:26">
+    <row r="33" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="3"/>
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
@@ -7253,7 +7936,7 @@
       <c r="Y33" s="3"/>
       <c r="Z33" s="3"/>
     </row>
-    <row r="34" spans="1:26">
+    <row r="34" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="3"/>
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
@@ -7281,7 +7964,7 @@
       <c r="Y34" s="3"/>
       <c r="Z34" s="3"/>
     </row>
-    <row r="35" spans="1:26">
+    <row r="35" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="3"/>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
@@ -7309,7 +7992,7 @@
       <c r="Y35" s="3"/>
       <c r="Z35" s="3"/>
     </row>
-    <row r="36" spans="1:26">
+    <row r="36" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="3"/>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
@@ -7337,7 +8020,7 @@
       <c r="Y36" s="3"/>
       <c r="Z36" s="3"/>
     </row>
-    <row r="37" spans="1:26">
+    <row r="37" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="3"/>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
@@ -7365,7 +8048,7 @@
       <c r="Y37" s="3"/>
       <c r="Z37" s="3"/>
     </row>
-    <row r="38" spans="1:26">
+    <row r="38" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="3"/>
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
@@ -7393,7 +8076,7 @@
       <c r="Y38" s="3"/>
       <c r="Z38" s="3"/>
     </row>
-    <row r="39" spans="1:26">
+    <row r="39" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="3"/>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
@@ -7421,7 +8104,7 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
     </row>
-    <row r="40" spans="1:26">
+    <row r="40" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="3"/>
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
@@ -7449,7 +8132,7 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
     </row>
-    <row r="41" spans="1:26">
+    <row r="41" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="3"/>
       <c r="B41" s="3"/>
       <c r="C41" s="3"/>
@@ -7477,7 +8160,7 @@
       <c r="Y41" s="3"/>
       <c r="Z41" s="3"/>
     </row>
-    <row r="42" spans="1:26">
+    <row r="42" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="3"/>
       <c r="B42" s="3"/>
       <c r="C42" s="3"/>
@@ -7505,7 +8188,7 @@
       <c r="Y42" s="3"/>
       <c r="Z42" s="3"/>
     </row>
-    <row r="43" spans="1:26">
+    <row r="43" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="3"/>
       <c r="B43" s="3"/>
       <c r="C43" s="3"/>
@@ -7533,7 +8216,7 @@
       <c r="Y43" s="3"/>
       <c r="Z43" s="3"/>
     </row>
-    <row r="44" spans="1:26">
+    <row r="44" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="3"/>
       <c r="B44" s="3"/>
       <c r="C44" s="3"/>
@@ -7561,7 +8244,7 @@
       <c r="Y44" s="3"/>
       <c r="Z44" s="3"/>
     </row>
-    <row r="45" spans="1:26">
+    <row r="45" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="3"/>
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
@@ -7589,7 +8272,7 @@
       <c r="Y45" s="3"/>
       <c r="Z45" s="3"/>
     </row>
-    <row r="46" spans="1:26">
+    <row r="46" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="3"/>
       <c r="B46" s="3"/>
       <c r="C46" s="3"/>
@@ -7617,7 +8300,7 @@
       <c r="Y46" s="3"/>
       <c r="Z46" s="3"/>
     </row>
-    <row r="47" spans="1:26">
+    <row r="47" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="3"/>
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
@@ -7645,7 +8328,7 @@
       <c r="Y47" s="3"/>
       <c r="Z47" s="3"/>
     </row>
-    <row r="48" spans="1:26">
+    <row r="48" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="3"/>
       <c r="B48" s="3"/>
       <c r="C48" s="3"/>
@@ -7673,7 +8356,7 @@
       <c r="Y48" s="3"/>
       <c r="Z48" s="3"/>
     </row>
-    <row r="49" spans="1:26">
+    <row r="49" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="3"/>
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
@@ -7701,7 +8384,7 @@
       <c r="Y49" s="3"/>
       <c r="Z49" s="3"/>
     </row>
-    <row r="50" spans="1:26">
+    <row r="50" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="3"/>
       <c r="B50" s="3"/>
       <c r="C50" s="3"/>
@@ -7729,7 +8412,7 @@
       <c r="Y50" s="3"/>
       <c r="Z50" s="3"/>
     </row>
-    <row r="51" spans="1:26">
+    <row r="51" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="3"/>
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
@@ -7757,7 +8440,7 @@
       <c r="Y51" s="3"/>
       <c r="Z51" s="3"/>
     </row>
-    <row r="52" spans="1:26">
+    <row r="52" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="3"/>
       <c r="B52" s="3"/>
       <c r="C52" s="3"/>
@@ -7785,7 +8468,7 @@
       <c r="Y52" s="3"/>
       <c r="Z52" s="3"/>
     </row>
-    <row r="53" spans="1:26">
+    <row r="53" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="3"/>
       <c r="B53" s="3"/>
       <c r="C53" s="3"/>
@@ -7813,7 +8496,7 @@
       <c r="Y53" s="3"/>
       <c r="Z53" s="3"/>
     </row>
-    <row r="54" spans="1:26">
+    <row r="54" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="3"/>
       <c r="B54" s="3"/>
       <c r="C54" s="3"/>
@@ -7841,7 +8524,7 @@
       <c r="Y54" s="3"/>
       <c r="Z54" s="3"/>
     </row>
-    <row r="55" spans="1:26">
+    <row r="55" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="3"/>
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
@@ -7869,7 +8552,7 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
     </row>
-    <row r="56" spans="1:26">
+    <row r="56" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="3"/>
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
@@ -7897,7 +8580,7 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
     </row>
-    <row r="57" spans="1:26">
+    <row r="57" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="3"/>
       <c r="B57" s="3"/>
       <c r="C57" s="3"/>
@@ -7925,7 +8608,7 @@
       <c r="Y57" s="3"/>
       <c r="Z57" s="3"/>
     </row>
-    <row r="58" spans="1:26">
+    <row r="58" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="3"/>
       <c r="B58" s="3"/>
       <c r="C58" s="3"/>
@@ -7953,7 +8636,7 @@
       <c r="Y58" s="3"/>
       <c r="Z58" s="3"/>
     </row>
-    <row r="59" spans="1:26">
+    <row r="59" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="3"/>
       <c r="B59" s="3"/>
       <c r="C59" s="3"/>
@@ -7981,7 +8664,7 @@
       <c r="Y59" s="3"/>
       <c r="Z59" s="3"/>
     </row>
-    <row r="60" spans="1:26">
+    <row r="60" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="3"/>
       <c r="B60" s="3"/>
       <c r="C60" s="3"/>
@@ -8013,60 +8696,45 @@
   <mergeCells count="1">
     <mergeCell ref="A1:S1"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:Z60"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.796875" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="13.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="32" customWidth="1"/>
-    <col min="2" max="5" width="14" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="2" style="1" width="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="27.15" customHeight="1">
-      <c r="A1" s="29" t="s">
+    <row r="1" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="29" t="s">
-        <v>27</v>
-      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
       <c r="N1" s="3"/>
       <c r="O1" s="3"/>
       <c r="P1" s="3"/>
@@ -8081,7 +8749,7 @@
       <c r="Y1" s="3"/>
       <c r="Z1" s="3"/>
     </row>
-    <row r="2" spans="1:26">
+    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -8109,20 +8777,20 @@
       <c r="Y2" s="3"/>
       <c r="Z2" s="3"/>
     </row>
-    <row r="3" spans="1:26">
-      <c r="A3" s="2" t="s">
+    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="5" t="s">
         <v>21</v>
       </c>
       <c r="F3" s="3"/>
@@ -8155,24 +8823,24 @@
       <c r="Y3" s="3"/>
       <c r="Z3" s="3"/>
     </row>
-    <row r="4" spans="1:26">
-      <c r="A4" s="4" t="s">
+    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B4" s="19">
-        <f>COUNT('Rohdaten Creme'!$B$4:$B$23)</f>
+      <c r="B4" s="23" t="n">
+        <f aca="false">COUNT('Rohdaten Creme'!$B$4:$B$23)</f>
         <v>20</v>
       </c>
-      <c r="C4" s="19">
-        <f>COUNT('Rohdaten Creme'!$C$4:$C$23)</f>
+      <c r="C4" s="23" t="n">
+        <f aca="false">COUNT('Rohdaten Creme'!$C$4:$C$23)</f>
         <v>20</v>
       </c>
-      <c r="D4" s="19">
-        <f>COUNT('Rohdaten Creme'!$D$4:$D$23)</f>
+      <c r="D4" s="23" t="n">
+        <f aca="false">COUNT('Rohdaten Creme'!$D$4:$D$23)</f>
         <v>20</v>
       </c>
-      <c r="E4" s="5">
-        <f>COUNT('Rohdaten Creme'!$E$4:$E$23)</f>
+      <c r="E4" s="8" t="n">
+        <f aca="false">COUNT('Rohdaten Creme'!$E$4:$E$23)</f>
         <v>20</v>
       </c>
       <c r="F4" s="3"/>
@@ -8186,17 +8854,17 @@
       <c r="N4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="O4" s="3">
-        <f>B7</f>
+      <c r="O4" s="29" t="n">
+        <f aca="false">B7</f>
         <v>5.35</v>
       </c>
       <c r="P4" s="3"/>
       <c r="Q4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="R4" s="3" t="e">
-        <f ca="1">B9</f>
-        <v>#NAME?</v>
+      <c r="R4" s="29" t="n">
+        <f aca="false">B9</f>
+        <v>2.18306882018965</v>
       </c>
       <c r="S4" s="3"/>
       <c r="T4" s="3"/>
@@ -8207,25 +8875,25 @@
       <c r="Y4" s="3"/>
       <c r="Z4" s="3"/>
     </row>
-    <row r="5" spans="1:26">
-      <c r="A5" s="6" t="s">
+    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="1" t="e">
-        <f ca="1">_xludf.MODE.SNGL('Rohdaten Creme'!$B$4:$B$23)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C5" s="1" t="e">
-        <f ca="1">_xludf.MODE.SNGL('Rohdaten Creme'!$C$4:$C$23)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="D5" s="1" t="e">
-        <f ca="1">_xludf.MODE.SNGL('Rohdaten Creme'!$D$4:$D$23)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="E5" s="7" t="e">
-        <f ca="1">_xludf.MODE.SNGL('Rohdaten Creme'!$E$4:$E$23)</f>
-        <v>#NAME?</v>
+      <c r="B5" s="24" t="n">
+        <f aca="false">MODE('Rohdaten Creme'!$B$4:$B$23)</f>
+        <v>6</v>
+      </c>
+      <c r="C5" s="24" t="n">
+        <f aca="false">MODE('Rohdaten Creme'!$C$4:$C$23)</f>
+        <v>1</v>
+      </c>
+      <c r="D5" s="24" t="n">
+        <f aca="false">MODE('Rohdaten Creme'!$D$4:$D$23)</f>
+        <v>7</v>
+      </c>
+      <c r="E5" s="10" t="n">
+        <f aca="false">MODE('Rohdaten Creme'!$E$4:$E$23)</f>
+        <v>2</v>
       </c>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
@@ -8238,17 +8906,17 @@
       <c r="N5" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="O5" s="3">
-        <f>C7</f>
+      <c r="O5" s="29" t="n">
+        <f aca="false">C7</f>
         <v>4.5</v>
       </c>
       <c r="P5" s="3"/>
       <c r="Q5" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="R5" s="3" t="e">
-        <f ca="1">C9</f>
-        <v>#NAME?</v>
+      <c r="R5" s="29" t="n">
+        <f aca="false">C9</f>
+        <v>2.9824045403173</v>
       </c>
       <c r="S5" s="3"/>
       <c r="T5" s="3"/>
@@ -8259,24 +8927,24 @@
       <c r="Y5" s="3"/>
       <c r="Z5" s="3"/>
     </row>
-    <row r="6" spans="1:26">
-      <c r="A6" s="6" t="s">
+    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="1">
-        <f>MEDIAN('Rohdaten Creme'!$B$4:$B$23)</f>
+      <c r="B6" s="24" t="n">
+        <f aca="false">MEDIAN('Rohdaten Creme'!$B$4:$B$23)</f>
         <v>6</v>
       </c>
-      <c r="C6" s="1">
-        <f>MEDIAN('Rohdaten Creme'!$C$4:$C$23)</f>
+      <c r="C6" s="24" t="n">
+        <f aca="false">MEDIAN('Rohdaten Creme'!$C$4:$C$23)</f>
         <v>3.5</v>
       </c>
-      <c r="D6" s="1">
-        <f>MEDIAN('Rohdaten Creme'!$D$4:$D$23)</f>
+      <c r="D6" s="24" t="n">
+        <f aca="false">MEDIAN('Rohdaten Creme'!$D$4:$D$23)</f>
         <v>7</v>
       </c>
-      <c r="E6" s="7">
-        <f>MEDIAN('Rohdaten Creme'!$E$4:$E$23)</f>
+      <c r="E6" s="10" t="n">
+        <f aca="false">MEDIAN('Rohdaten Creme'!$E$4:$E$23)</f>
         <v>2</v>
       </c>
       <c r="F6" s="3"/>
@@ -8290,17 +8958,17 @@
       <c r="N6" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="O6" s="3">
-        <f>D7</f>
+      <c r="O6" s="29" t="n">
+        <f aca="false">D7</f>
         <v>6.1</v>
       </c>
       <c r="P6" s="3"/>
       <c r="Q6" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="R6" s="3" t="e">
-        <f ca="1">D9</f>
-        <v>#NAME?</v>
+      <c r="R6" s="29" t="n">
+        <f aca="false">D9</f>
+        <v>2.02354561157026</v>
       </c>
       <c r="S6" s="3"/>
       <c r="T6" s="3"/>
@@ -8311,24 +8979,24 @@
       <c r="Y6" s="3"/>
       <c r="Z6" s="3"/>
     </row>
-    <row r="7" spans="1:26">
-      <c r="A7" s="6" t="s">
+    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="B7" s="24">
-        <f>AVERAGE('Rohdaten Creme'!$B$4:$B$23)</f>
+      <c r="B7" s="30" t="n">
+        <f aca="false">AVERAGE('Rohdaten Creme'!$B$4:$B$23)</f>
         <v>5.35</v>
       </c>
-      <c r="C7" s="24">
-        <f>AVERAGE('Rohdaten Creme'!$C$4:$C$23)</f>
+      <c r="C7" s="30" t="n">
+        <f aca="false">AVERAGE('Rohdaten Creme'!$C$4:$C$23)</f>
         <v>4.5</v>
       </c>
-      <c r="D7" s="24">
-        <f>AVERAGE('Rohdaten Creme'!$D$4:$D$23)</f>
+      <c r="D7" s="30" t="n">
+        <f aca="false">AVERAGE('Rohdaten Creme'!$D$4:$D$23)</f>
         <v>6.1</v>
       </c>
-      <c r="E7" s="25">
-        <f>AVERAGE('Rohdaten Creme'!$E$4:$E$23)</f>
+      <c r="E7" s="31" t="n">
+        <f aca="false">AVERAGE('Rohdaten Creme'!$E$4:$E$23)</f>
         <v>2.35</v>
       </c>
       <c r="F7" s="3"/>
@@ -8342,17 +9010,17 @@
       <c r="N7" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="O7" s="3">
-        <f>E7</f>
+      <c r="O7" s="29" t="n">
+        <f aca="false">E7</f>
         <v>2.35</v>
       </c>
       <c r="P7" s="3"/>
       <c r="Q7" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="R7" s="3" t="e">
-        <f ca="1">E9</f>
-        <v>#NAME?</v>
+      <c r="R7" s="29" t="n">
+        <f aca="false">E9</f>
+        <v>0.875093979915421</v>
       </c>
       <c r="S7" s="3"/>
       <c r="T7" s="3"/>
@@ -8363,25 +9031,25 @@
       <c r="Y7" s="3"/>
       <c r="Z7" s="3"/>
     </row>
-    <row r="8" spans="1:26">
-      <c r="A8" s="6" t="s">
+    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="B8" s="24" t="e">
-        <f ca="1">_xludf.VAR.S('Rohdaten Creme'!$B$4:$B$23)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C8" s="24" t="e">
-        <f ca="1">_xludf.VAR.S('Rohdaten Creme'!$C$4:$C$23)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="D8" s="24" t="e">
-        <f ca="1">_xludf.VAR.S('Rohdaten Creme'!$D$4:$D$23)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="E8" s="25" t="e">
-        <f ca="1">_xludf.VAR.S('Rohdaten Creme'!$E$4:$E$23)</f>
-        <v>#NAME?</v>
+      <c r="B8" s="30" t="n">
+        <f aca="false">VAR('Rohdaten Creme'!$B$4:$B$23)</f>
+        <v>4.76578947368421</v>
+      </c>
+      <c r="C8" s="30" t="n">
+        <f aca="false">VAR('Rohdaten Creme'!$C$4:$C$23)</f>
+        <v>8.89473684210526</v>
+      </c>
+      <c r="D8" s="30" t="n">
+        <f aca="false">VAR('Rohdaten Creme'!$D$4:$D$23)</f>
+        <v>4.09473684210526</v>
+      </c>
+      <c r="E8" s="31" t="n">
+        <f aca="false">VAR('Rohdaten Creme'!$E$4:$E$23)</f>
+        <v>0.765789473684211</v>
       </c>
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
@@ -8405,25 +9073,25 @@
       <c r="Y8" s="3"/>
       <c r="Z8" s="3"/>
     </row>
-    <row r="9" spans="1:26">
-      <c r="A9" s="6" t="s">
+    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="24" t="e">
-        <f ca="1">_xludf.STDEV.S('Rohdaten Creme'!$B$4:$B$23)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C9" s="24" t="e">
-        <f ca="1">_xludf.STDEV.S('Rohdaten Creme'!$C$4:$C$23)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="D9" s="24" t="e">
-        <f ca="1">_xludf.STDEV.S('Rohdaten Creme'!$D$4:$D$23)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="E9" s="25" t="e">
-        <f ca="1">_xludf.STDEV.S('Rohdaten Creme'!$E$4:$E$23)</f>
-        <v>#NAME?</v>
+      <c r="B9" s="30" t="n">
+        <f aca="false">STDEV('Rohdaten Creme'!$B$4:$B$23)</f>
+        <v>2.18306882018965</v>
+      </c>
+      <c r="C9" s="30" t="n">
+        <f aca="false">STDEV('Rohdaten Creme'!$C$4:$C$23)</f>
+        <v>2.9824045403173</v>
+      </c>
+      <c r="D9" s="30" t="n">
+        <f aca="false">STDEV('Rohdaten Creme'!$D$4:$D$23)</f>
+        <v>2.02354561157026</v>
+      </c>
+      <c r="E9" s="31" t="n">
+        <f aca="false">STDEV('Rohdaten Creme'!$E$4:$E$23)</f>
+        <v>0.875093979915421</v>
       </c>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
@@ -8447,24 +9115,24 @@
       <c r="Y9" s="3"/>
       <c r="Z9" s="3"/>
     </row>
-    <row r="10" spans="1:26">
-      <c r="A10" s="6" t="s">
+    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="B10" s="1">
-        <f>MIN('Rohdaten Creme'!$B$4:$B$23)</f>
+      <c r="B10" s="24" t="n">
+        <f aca="false">MIN('Rohdaten Creme'!$B$4:$B$23)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="1">
-        <f>MIN('Rohdaten Creme'!$C$4:$C$23)</f>
+      <c r="C10" s="24" t="n">
+        <f aca="false">MIN('Rohdaten Creme'!$C$4:$C$23)</f>
         <v>1</v>
       </c>
-      <c r="D10" s="1">
-        <f>MIN('Rohdaten Creme'!$D$4:$D$23)</f>
+      <c r="D10" s="24" t="n">
+        <f aca="false">MIN('Rohdaten Creme'!$D$4:$D$23)</f>
         <v>2</v>
       </c>
-      <c r="E10" s="7">
-        <f>MIN('Rohdaten Creme'!$E$4:$E$23)</f>
+      <c r="E10" s="10" t="n">
+        <f aca="false">MIN('Rohdaten Creme'!$E$4:$E$23)</f>
         <v>1</v>
       </c>
       <c r="F10" s="3"/>
@@ -8489,24 +9157,24 @@
       <c r="Y10" s="3"/>
       <c r="Z10" s="3"/>
     </row>
-    <row r="11" spans="1:26">
-      <c r="A11" s="8" t="s">
+    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="B11" s="20">
-        <f>MAX('Rohdaten Creme'!$B$4:$B$23)</f>
+      <c r="B11" s="25" t="n">
+        <f aca="false">MAX('Rohdaten Creme'!$B$4:$B$23)</f>
         <v>9</v>
       </c>
-      <c r="C11" s="20">
-        <f>MAX('Rohdaten Creme'!$C$4:$C$23)</f>
+      <c r="C11" s="25" t="n">
+        <f aca="false">MAX('Rohdaten Creme'!$C$4:$C$23)</f>
         <v>9</v>
       </c>
-      <c r="D11" s="20">
-        <f>MAX('Rohdaten Creme'!$D$4:$D$23)</f>
+      <c r="D11" s="25" t="n">
+        <f aca="false">MAX('Rohdaten Creme'!$D$4:$D$23)</f>
         <v>9</v>
       </c>
-      <c r="E11" s="9">
-        <f>MAX('Rohdaten Creme'!$E$4:$E$23)</f>
+      <c r="E11" s="12" t="n">
+        <f aca="false">MAX('Rohdaten Creme'!$E$4:$E$23)</f>
         <v>4</v>
       </c>
       <c r="F11" s="3"/>
@@ -8531,7 +9199,7 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
     </row>
-    <row r="12" spans="1:26">
+    <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -8559,14 +9227,14 @@
       <c r="Y12" s="3"/>
       <c r="Z12" s="3"/>
     </row>
-    <row r="13" spans="1:26">
-      <c r="A13" s="33" t="s">
+    <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="B13" s="33"/>
-      <c r="C13" s="33"/>
-      <c r="D13" s="33"/>
-      <c r="E13" s="33"/>
+      <c r="B13" s="32"/>
+      <c r="C13" s="32"/>
+      <c r="D13" s="32"/>
+      <c r="E13" s="32"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
@@ -8589,12 +9257,12 @@
       <c r="Y13" s="3"/>
       <c r="Z13" s="3"/>
     </row>
-    <row r="14" spans="1:26">
-      <c r="A14" s="33"/>
-      <c r="B14" s="33"/>
-      <c r="C14" s="33"/>
-      <c r="D14" s="33"/>
-      <c r="E14" s="33"/>
+    <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="32"/>
+      <c r="B14" s="32"/>
+      <c r="C14" s="32"/>
+      <c r="D14" s="32"/>
+      <c r="E14" s="32"/>
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
@@ -8617,7 +9285,7 @@
       <c r="Y14" s="3"/>
       <c r="Z14" s="3"/>
     </row>
-    <row r="15" spans="1:26">
+    <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -8645,7 +9313,7 @@
       <c r="Y15" s="3"/>
       <c r="Z15" s="3"/>
     </row>
-    <row r="16" spans="1:26">
+    <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
@@ -8673,7 +9341,7 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
     </row>
-    <row r="17" spans="1:26">
+    <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3"/>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
@@ -8701,7 +9369,7 @@
       <c r="Y17" s="3"/>
       <c r="Z17" s="3"/>
     </row>
-    <row r="18" spans="1:26">
+    <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3"/>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -8729,7 +9397,7 @@
       <c r="Y18" s="3"/>
       <c r="Z18" s="3"/>
     </row>
-    <row r="19" spans="1:26">
+    <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="3"/>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
@@ -8757,7 +9425,7 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
     </row>
-    <row r="20" spans="1:26">
+    <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="3"/>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
@@ -8785,7 +9453,7 @@
       <c r="Y20" s="3"/>
       <c r="Z20" s="3"/>
     </row>
-    <row r="21" spans="1:26">
+    <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="3"/>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -8813,7 +9481,7 @@
       <c r="Y21" s="3"/>
       <c r="Z21" s="3"/>
     </row>
-    <row r="22" spans="1:26">
+    <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="3"/>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
@@ -8841,7 +9509,7 @@
       <c r="Y22" s="3"/>
       <c r="Z22" s="3"/>
     </row>
-    <row r="23" spans="1:26">
+    <row r="23" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="3"/>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
@@ -8869,7 +9537,7 @@
       <c r="Y23" s="3"/>
       <c r="Z23" s="3"/>
     </row>
-    <row r="24" spans="1:26">
+    <row r="24" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3"/>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
@@ -8897,7 +9565,7 @@
       <c r="Y24" s="3"/>
       <c r="Z24" s="3"/>
     </row>
-    <row r="25" spans="1:26">
+    <row r="25" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="3"/>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
@@ -8925,7 +9593,7 @@
       <c r="Y25" s="3"/>
       <c r="Z25" s="3"/>
     </row>
-    <row r="26" spans="1:26">
+    <row r="26" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3"/>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
@@ -8953,7 +9621,7 @@
       <c r="Y26" s="3"/>
       <c r="Z26" s="3"/>
     </row>
-    <row r="27" spans="1:26">
+    <row r="27" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="3"/>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
@@ -8981,7 +9649,7 @@
       <c r="Y27" s="3"/>
       <c r="Z27" s="3"/>
     </row>
-    <row r="28" spans="1:26">
+    <row r="28" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="3"/>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
@@ -9009,7 +9677,7 @@
       <c r="Y28" s="3"/>
       <c r="Z28" s="3"/>
     </row>
-    <row r="29" spans="1:26">
+    <row r="29" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="3"/>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
@@ -9037,7 +9705,7 @@
       <c r="Y29" s="3"/>
       <c r="Z29" s="3"/>
     </row>
-    <row r="30" spans="1:26">
+    <row r="30" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="3"/>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
@@ -9065,7 +9733,7 @@
       <c r="Y30" s="3"/>
       <c r="Z30" s="3"/>
     </row>
-    <row r="31" spans="1:26">
+    <row r="31" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3"/>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
@@ -9093,7 +9761,7 @@
       <c r="Y31" s="3"/>
       <c r="Z31" s="3"/>
     </row>
-    <row r="32" spans="1:26">
+    <row r="32" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="3"/>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
@@ -9121,7 +9789,7 @@
       <c r="Y32" s="3"/>
       <c r="Z32" s="3"/>
     </row>
-    <row r="33" spans="1:26">
+    <row r="33" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="3"/>
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
@@ -9149,7 +9817,7 @@
       <c r="Y33" s="3"/>
       <c r="Z33" s="3"/>
     </row>
-    <row r="34" spans="1:26">
+    <row r="34" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="3"/>
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
@@ -9177,7 +9845,7 @@
       <c r="Y34" s="3"/>
       <c r="Z34" s="3"/>
     </row>
-    <row r="35" spans="1:26">
+    <row r="35" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="3"/>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
@@ -9205,7 +9873,7 @@
       <c r="Y35" s="3"/>
       <c r="Z35" s="3"/>
     </row>
-    <row r="36" spans="1:26">
+    <row r="36" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="3"/>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
@@ -9233,7 +9901,7 @@
       <c r="Y36" s="3"/>
       <c r="Z36" s="3"/>
     </row>
-    <row r="37" spans="1:26">
+    <row r="37" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="3"/>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
@@ -9261,7 +9929,7 @@
       <c r="Y37" s="3"/>
       <c r="Z37" s="3"/>
     </row>
-    <row r="38" spans="1:26">
+    <row r="38" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="3"/>
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
@@ -9289,7 +9957,7 @@
       <c r="Y38" s="3"/>
       <c r="Z38" s="3"/>
     </row>
-    <row r="39" spans="1:26">
+    <row r="39" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="3"/>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
@@ -9317,7 +9985,7 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
     </row>
-    <row r="40" spans="1:26">
+    <row r="40" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="3"/>
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
@@ -9345,7 +10013,7 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
     </row>
-    <row r="41" spans="1:26">
+    <row r="41" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="3"/>
       <c r="B41" s="3"/>
       <c r="C41" s="3"/>
@@ -9373,7 +10041,7 @@
       <c r="Y41" s="3"/>
       <c r="Z41" s="3"/>
     </row>
-    <row r="42" spans="1:26">
+    <row r="42" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="3"/>
       <c r="B42" s="3"/>
       <c r="C42" s="3"/>
@@ -9401,7 +10069,7 @@
       <c r="Y42" s="3"/>
       <c r="Z42" s="3"/>
     </row>
-    <row r="43" spans="1:26">
+    <row r="43" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="3"/>
       <c r="B43" s="3"/>
       <c r="C43" s="3"/>
@@ -9429,7 +10097,7 @@
       <c r="Y43" s="3"/>
       <c r="Z43" s="3"/>
     </row>
-    <row r="44" spans="1:26">
+    <row r="44" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="3"/>
       <c r="B44" s="3"/>
       <c r="C44" s="3"/>
@@ -9457,7 +10125,7 @@
       <c r="Y44" s="3"/>
       <c r="Z44" s="3"/>
     </row>
-    <row r="45" spans="1:26">
+    <row r="45" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="3"/>
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
@@ -9485,7 +10153,7 @@
       <c r="Y45" s="3"/>
       <c r="Z45" s="3"/>
     </row>
-    <row r="46" spans="1:26">
+    <row r="46" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="3"/>
       <c r="B46" s="3"/>
       <c r="C46" s="3"/>
@@ -9513,7 +10181,7 @@
       <c r="Y46" s="3"/>
       <c r="Z46" s="3"/>
     </row>
-    <row r="47" spans="1:26">
+    <row r="47" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="3"/>
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
@@ -9541,7 +10209,7 @@
       <c r="Y47" s="3"/>
       <c r="Z47" s="3"/>
     </row>
-    <row r="48" spans="1:26">
+    <row r="48" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="3"/>
       <c r="B48" s="3"/>
       <c r="C48" s="3"/>
@@ -9569,7 +10237,7 @@
       <c r="Y48" s="3"/>
       <c r="Z48" s="3"/>
     </row>
-    <row r="49" spans="1:26">
+    <row r="49" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="3"/>
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
@@ -9597,7 +10265,7 @@
       <c r="Y49" s="3"/>
       <c r="Z49" s="3"/>
     </row>
-    <row r="50" spans="1:26">
+    <row r="50" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="3"/>
       <c r="B50" s="3"/>
       <c r="C50" s="3"/>
@@ -9625,7 +10293,7 @@
       <c r="Y50" s="3"/>
       <c r="Z50" s="3"/>
     </row>
-    <row r="51" spans="1:26">
+    <row r="51" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="3"/>
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
@@ -9653,7 +10321,7 @@
       <c r="Y51" s="3"/>
       <c r="Z51" s="3"/>
     </row>
-    <row r="52" spans="1:26">
+    <row r="52" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="3"/>
       <c r="B52" s="3"/>
       <c r="C52" s="3"/>
@@ -9681,7 +10349,7 @@
       <c r="Y52" s="3"/>
       <c r="Z52" s="3"/>
     </row>
-    <row r="53" spans="1:26">
+    <row r="53" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="3"/>
       <c r="B53" s="3"/>
       <c r="C53" s="3"/>
@@ -9709,7 +10377,7 @@
       <c r="Y53" s="3"/>
       <c r="Z53" s="3"/>
     </row>
-    <row r="54" spans="1:26">
+    <row r="54" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="3"/>
       <c r="B54" s="3"/>
       <c r="C54" s="3"/>
@@ -9737,7 +10405,7 @@
       <c r="Y54" s="3"/>
       <c r="Z54" s="3"/>
     </row>
-    <row r="55" spans="1:26">
+    <row r="55" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="3"/>
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
@@ -9765,7 +10433,7 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
     </row>
-    <row r="56" spans="1:26">
+    <row r="56" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="3"/>
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
@@ -9793,7 +10461,7 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
     </row>
-    <row r="57" spans="1:26">
+    <row r="57" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="3"/>
       <c r="B57" s="3"/>
       <c r="C57" s="3"/>
@@ -9821,7 +10489,7 @@
       <c r="Y57" s="3"/>
       <c r="Z57" s="3"/>
     </row>
-    <row r="58" spans="1:26">
+    <row r="58" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="3"/>
       <c r="B58" s="3"/>
       <c r="C58" s="3"/>
@@ -9849,7 +10517,7 @@
       <c r="Y58" s="3"/>
       <c r="Z58" s="3"/>
     </row>
-    <row r="59" spans="1:26">
+    <row r="59" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="3"/>
       <c r="B59" s="3"/>
       <c r="C59" s="3"/>
@@ -9877,7 +10545,7 @@
       <c r="Y59" s="3"/>
       <c r="Z59" s="3"/>
     </row>
-    <row r="60" spans="1:26">
+    <row r="60" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="3"/>
       <c r="B60" s="3"/>
       <c r="C60" s="3"/>
@@ -9910,48 +10578,43 @@
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="A13:E14"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:Z60"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.796875" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="13.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="22" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="22"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="27.15" customHeight="1">
-      <c r="A1" s="29" t="s">
+    <row r="1" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="29" t="s">
-        <v>41</v>
-      </c>
-      <c r="C1" s="29" t="s">
-        <v>41</v>
-      </c>
-      <c r="D1" s="29" t="s">
-        <v>41</v>
-      </c>
-      <c r="E1" s="29" t="s">
-        <v>41</v>
-      </c>
-      <c r="F1" s="29" t="s">
-        <v>41</v>
-      </c>
-      <c r="G1" s="29" t="s">
-        <v>41</v>
-      </c>
-      <c r="H1" s="29" t="s">
-        <v>41</v>
-      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
       <c r="K1" s="3"/>
@@ -9971,7 +10634,7 @@
       <c r="Y1" s="3"/>
       <c r="Z1" s="3"/>
     </row>
-    <row r="2" spans="1:26">
+    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -9999,23 +10662,23 @@
       <c r="Y2" s="3"/>
       <c r="Z2" s="3"/>
     </row>
-    <row r="3" spans="1:26">
-      <c r="A3" s="2" t="s">
+    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="5" t="s">
         <v>47</v>
       </c>
       <c r="G3" s="3"/>
@@ -10039,23 +10702,23 @@
       <c r="Y3" s="3"/>
       <c r="Z3" s="3"/>
     </row>
-    <row r="4" spans="1:26">
-      <c r="A4" s="4" t="s">
+    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="D4" s="26">
-        <v>0.46129999999999999</v>
-      </c>
-      <c r="E4" s="19" t="s">
+      <c r="D4" s="33" t="n">
+        <v>0.4613</v>
+      </c>
+      <c r="E4" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="8" t="s">
         <v>52</v>
       </c>
       <c r="G4" s="3"/>
@@ -10079,23 +10742,23 @@
       <c r="Y4" s="3"/>
       <c r="Z4" s="3"/>
     </row>
-    <row r="5" spans="1:26">
-      <c r="A5" s="6" t="s">
+    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="D5" s="27">
-        <v>0.23380000000000001</v>
-      </c>
-      <c r="E5" s="1" t="s">
+      <c r="D5" s="34" t="n">
+        <v>0.2338</v>
+      </c>
+      <c r="E5" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="10" t="s">
         <v>52</v>
       </c>
       <c r="G5" s="3"/>
@@ -10119,23 +10782,23 @@
       <c r="Y5" s="3"/>
       <c r="Z5" s="3"/>
     </row>
-    <row r="6" spans="1:26">
-      <c r="A6" s="6" t="s">
+    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="D6" s="27">
-        <v>5.8999999999999998E-5</v>
-      </c>
-      <c r="E6" s="1" t="s">
+      <c r="D6" s="34" t="n">
+        <v>5.9E-005</v>
+      </c>
+      <c r="E6" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="10" t="s">
         <v>56</v>
       </c>
       <c r="G6" s="3"/>
@@ -10159,23 +10822,23 @@
       <c r="Y6" s="3"/>
       <c r="Z6" s="3"/>
     </row>
-    <row r="7" spans="1:26">
-      <c r="A7" s="6" t="s">
+    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="D7" s="27">
-        <v>7.3599999999999999E-2</v>
-      </c>
-      <c r="E7" s="1" t="s">
+      <c r="D7" s="34" t="n">
+        <v>0.0736</v>
+      </c>
+      <c r="E7" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="10" t="s">
         <v>52</v>
       </c>
       <c r="G7" s="3"/>
@@ -10199,23 +10862,23 @@
       <c r="Y7" s="3"/>
       <c r="Z7" s="3"/>
     </row>
-    <row r="8" spans="1:26">
-      <c r="A8" s="6" t="s">
+    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="D8" s="27">
-        <v>1.9999999999999999E-6</v>
-      </c>
-      <c r="E8" s="1" t="s">
+      <c r="D8" s="34" t="n">
+        <v>2E-006</v>
+      </c>
+      <c r="E8" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="10" t="s">
         <v>56</v>
       </c>
       <c r="G8" s="3"/>
@@ -10239,23 +10902,23 @@
       <c r="Y8" s="3"/>
       <c r="Z8" s="3"/>
     </row>
-    <row r="9" spans="1:26">
-      <c r="A9" s="6" t="s">
+    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="D9" s="27">
-        <v>0.34229999999999999</v>
-      </c>
-      <c r="E9" s="1" t="s">
+      <c r="D9" s="34" t="n">
+        <v>0.3423</v>
+      </c>
+      <c r="E9" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="10" t="s">
         <v>52</v>
       </c>
       <c r="G9" s="3"/>
@@ -10279,23 +10942,23 @@
       <c r="Y9" s="3"/>
       <c r="Z9" s="3"/>
     </row>
-    <row r="10" spans="1:26">
-      <c r="A10" s="8" t="s">
+    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="B10" s="20" t="s">
+      <c r="B10" s="25" t="s">
         <v>59</v>
       </c>
-      <c r="C10" s="20" t="s">
+      <c r="C10" s="25" t="s">
         <v>60</v>
       </c>
-      <c r="D10" s="28">
-        <v>4.0999999999999999E-4</v>
-      </c>
-      <c r="E10" s="20" t="s">
+      <c r="D10" s="35" t="n">
+        <v>0.00041</v>
+      </c>
+      <c r="E10" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="F10" s="12" t="s">
         <v>56</v>
       </c>
       <c r="G10" s="3"/>
@@ -10319,7 +10982,7 @@
       <c r="Y10" s="3"/>
       <c r="Z10" s="3"/>
     </row>
-    <row r="11" spans="1:26">
+    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
@@ -10347,15 +11010,15 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
     </row>
-    <row r="12" spans="1:26">
-      <c r="A12" s="31" t="s">
+    <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="31"/>
-      <c r="C12" s="31"/>
-      <c r="D12" s="31"/>
-      <c r="E12" s="31"/>
-      <c r="F12" s="31"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
@@ -10377,13 +11040,13 @@
       <c r="Y12" s="3"/>
       <c r="Z12" s="3"/>
     </row>
-    <row r="13" spans="1:26">
-      <c r="A13" s="31"/>
-      <c r="B13" s="31"/>
-      <c r="C13" s="31"/>
-      <c r="D13" s="31"/>
-      <c r="E13" s="31"/>
-      <c r="F13" s="31"/>
+    <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
@@ -10405,13 +11068,13 @@
       <c r="Y13" s="3"/>
       <c r="Z13" s="3"/>
     </row>
-    <row r="14" spans="1:26">
-      <c r="A14" s="31"/>
-      <c r="B14" s="31"/>
-      <c r="C14" s="31"/>
-      <c r="D14" s="31"/>
-      <c r="E14" s="31"/>
-      <c r="F14" s="31"/>
+    <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="6"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
@@ -10433,7 +11096,7 @@
       <c r="Y14" s="3"/>
       <c r="Z14" s="3"/>
     </row>
-    <row r="15" spans="1:26">
+    <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -10461,7 +11124,7 @@
       <c r="Y15" s="3"/>
       <c r="Z15" s="3"/>
     </row>
-    <row r="16" spans="1:26">
+    <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
@@ -10489,7 +11152,7 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
     </row>
-    <row r="17" spans="1:26">
+    <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3"/>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
@@ -10517,7 +11180,7 @@
       <c r="Y17" s="3"/>
       <c r="Z17" s="3"/>
     </row>
-    <row r="18" spans="1:26">
+    <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3"/>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -10545,7 +11208,7 @@
       <c r="Y18" s="3"/>
       <c r="Z18" s="3"/>
     </row>
-    <row r="19" spans="1:26">
+    <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="3"/>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
@@ -10573,7 +11236,7 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
     </row>
-    <row r="20" spans="1:26">
+    <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="3"/>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
@@ -10601,7 +11264,7 @@
       <c r="Y20" s="3"/>
       <c r="Z20" s="3"/>
     </row>
-    <row r="21" spans="1:26">
+    <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="3"/>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -10629,7 +11292,7 @@
       <c r="Y21" s="3"/>
       <c r="Z21" s="3"/>
     </row>
-    <row r="22" spans="1:26">
+    <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="3"/>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
@@ -10657,7 +11320,7 @@
       <c r="Y22" s="3"/>
       <c r="Z22" s="3"/>
     </row>
-    <row r="23" spans="1:26">
+    <row r="23" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="3"/>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
@@ -10685,7 +11348,7 @@
       <c r="Y23" s="3"/>
       <c r="Z23" s="3"/>
     </row>
-    <row r="24" spans="1:26">
+    <row r="24" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3"/>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
@@ -10713,7 +11376,7 @@
       <c r="Y24" s="3"/>
       <c r="Z24" s="3"/>
     </row>
-    <row r="25" spans="1:26">
+    <row r="25" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="3"/>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
@@ -10741,7 +11404,7 @@
       <c r="Y25" s="3"/>
       <c r="Z25" s="3"/>
     </row>
-    <row r="26" spans="1:26">
+    <row r="26" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3"/>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
@@ -10769,7 +11432,7 @@
       <c r="Y26" s="3"/>
       <c r="Z26" s="3"/>
     </row>
-    <row r="27" spans="1:26">
+    <row r="27" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="3"/>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
@@ -10797,7 +11460,7 @@
       <c r="Y27" s="3"/>
       <c r="Z27" s="3"/>
     </row>
-    <row r="28" spans="1:26">
+    <row r="28" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="3"/>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
@@ -10825,7 +11488,7 @@
       <c r="Y28" s="3"/>
       <c r="Z28" s="3"/>
     </row>
-    <row r="29" spans="1:26">
+    <row r="29" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="3"/>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
@@ -10853,7 +11516,7 @@
       <c r="Y29" s="3"/>
       <c r="Z29" s="3"/>
     </row>
-    <row r="30" spans="1:26">
+    <row r="30" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="3"/>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
@@ -10881,7 +11544,7 @@
       <c r="Y30" s="3"/>
       <c r="Z30" s="3"/>
     </row>
-    <row r="31" spans="1:26">
+    <row r="31" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3"/>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
@@ -10909,7 +11572,7 @@
       <c r="Y31" s="3"/>
       <c r="Z31" s="3"/>
     </row>
-    <row r="32" spans="1:26">
+    <row r="32" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="3"/>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
@@ -10937,7 +11600,7 @@
       <c r="Y32" s="3"/>
       <c r="Z32" s="3"/>
     </row>
-    <row r="33" spans="1:26">
+    <row r="33" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="3"/>
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
@@ -10965,7 +11628,7 @@
       <c r="Y33" s="3"/>
       <c r="Z33" s="3"/>
     </row>
-    <row r="34" spans="1:26">
+    <row r="34" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="3"/>
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
@@ -10993,7 +11656,7 @@
       <c r="Y34" s="3"/>
       <c r="Z34" s="3"/>
     </row>
-    <row r="35" spans="1:26">
+    <row r="35" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="3"/>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
@@ -11021,7 +11684,7 @@
       <c r="Y35" s="3"/>
       <c r="Z35" s="3"/>
     </row>
-    <row r="36" spans="1:26">
+    <row r="36" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="3"/>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
@@ -11049,7 +11712,7 @@
       <c r="Y36" s="3"/>
       <c r="Z36" s="3"/>
     </row>
-    <row r="37" spans="1:26">
+    <row r="37" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="3"/>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
@@ -11077,7 +11740,7 @@
       <c r="Y37" s="3"/>
       <c r="Z37" s="3"/>
     </row>
-    <row r="38" spans="1:26">
+    <row r="38" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="3"/>
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
@@ -11105,7 +11768,7 @@
       <c r="Y38" s="3"/>
       <c r="Z38" s="3"/>
     </row>
-    <row r="39" spans="1:26">
+    <row r="39" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="3"/>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
@@ -11133,7 +11796,7 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
     </row>
-    <row r="40" spans="1:26">
+    <row r="40" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="3"/>
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
@@ -11161,7 +11824,7 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
     </row>
-    <row r="41" spans="1:26">
+    <row r="41" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="3"/>
       <c r="B41" s="3"/>
       <c r="C41" s="3"/>
@@ -11189,7 +11852,7 @@
       <c r="Y41" s="3"/>
       <c r="Z41" s="3"/>
     </row>
-    <row r="42" spans="1:26">
+    <row r="42" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="3"/>
       <c r="B42" s="3"/>
       <c r="C42" s="3"/>
@@ -11217,7 +11880,7 @@
       <c r="Y42" s="3"/>
       <c r="Z42" s="3"/>
     </row>
-    <row r="43" spans="1:26">
+    <row r="43" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="3"/>
       <c r="B43" s="3"/>
       <c r="C43" s="3"/>
@@ -11245,7 +11908,7 @@
       <c r="Y43" s="3"/>
       <c r="Z43" s="3"/>
     </row>
-    <row r="44" spans="1:26">
+    <row r="44" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="3"/>
       <c r="B44" s="3"/>
       <c r="C44" s="3"/>
@@ -11273,7 +11936,7 @@
       <c r="Y44" s="3"/>
       <c r="Z44" s="3"/>
     </row>
-    <row r="45" spans="1:26">
+    <row r="45" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="3"/>
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
@@ -11301,7 +11964,7 @@
       <c r="Y45" s="3"/>
       <c r="Z45" s="3"/>
     </row>
-    <row r="46" spans="1:26">
+    <row r="46" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="3"/>
       <c r="B46" s="3"/>
       <c r="C46" s="3"/>
@@ -11329,7 +11992,7 @@
       <c r="Y46" s="3"/>
       <c r="Z46" s="3"/>
     </row>
-    <row r="47" spans="1:26">
+    <row r="47" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="3"/>
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
@@ -11357,7 +12020,7 @@
       <c r="Y47" s="3"/>
       <c r="Z47" s="3"/>
     </row>
-    <row r="48" spans="1:26">
+    <row r="48" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="3"/>
       <c r="B48" s="3"/>
       <c r="C48" s="3"/>
@@ -11385,7 +12048,7 @@
       <c r="Y48" s="3"/>
       <c r="Z48" s="3"/>
     </row>
-    <row r="49" spans="1:26">
+    <row r="49" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="3"/>
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
@@ -11413,7 +12076,7 @@
       <c r="Y49" s="3"/>
       <c r="Z49" s="3"/>
     </row>
-    <row r="50" spans="1:26">
+    <row r="50" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="3"/>
       <c r="B50" s="3"/>
       <c r="C50" s="3"/>
@@ -11441,7 +12104,7 @@
       <c r="Y50" s="3"/>
       <c r="Z50" s="3"/>
     </row>
-    <row r="51" spans="1:26">
+    <row r="51" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="3"/>
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
@@ -11469,7 +12132,7 @@
       <c r="Y51" s="3"/>
       <c r="Z51" s="3"/>
     </row>
-    <row r="52" spans="1:26">
+    <row r="52" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="3"/>
       <c r="B52" s="3"/>
       <c r="C52" s="3"/>
@@ -11497,7 +12160,7 @@
       <c r="Y52" s="3"/>
       <c r="Z52" s="3"/>
     </row>
-    <row r="53" spans="1:26">
+    <row r="53" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="3"/>
       <c r="B53" s="3"/>
       <c r="C53" s="3"/>
@@ -11525,7 +12188,7 @@
       <c r="Y53" s="3"/>
       <c r="Z53" s="3"/>
     </row>
-    <row r="54" spans="1:26">
+    <row r="54" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="3"/>
       <c r="B54" s="3"/>
       <c r="C54" s="3"/>
@@ -11553,7 +12216,7 @@
       <c r="Y54" s="3"/>
       <c r="Z54" s="3"/>
     </row>
-    <row r="55" spans="1:26">
+    <row r="55" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="3"/>
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
@@ -11581,7 +12244,7 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
     </row>
-    <row r="56" spans="1:26">
+    <row r="56" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="3"/>
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
@@ -11609,7 +12272,7 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
     </row>
-    <row r="57" spans="1:26">
+    <row r="57" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="3"/>
       <c r="B57" s="3"/>
       <c r="C57" s="3"/>
@@ -11637,7 +12300,7 @@
       <c r="Y57" s="3"/>
       <c r="Z57" s="3"/>
     </row>
-    <row r="58" spans="1:26">
+    <row r="58" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="3"/>
       <c r="B58" s="3"/>
       <c r="C58" s="3"/>
@@ -11665,7 +12328,7 @@
       <c r="Y58" s="3"/>
       <c r="Z58" s="3"/>
     </row>
-    <row r="59" spans="1:26">
+    <row r="59" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="3"/>
       <c r="B59" s="3"/>
       <c r="C59" s="3"/>
@@ -11693,7 +12356,7 @@
       <c r="Y59" s="3"/>
       <c r="Z59" s="3"/>
     </row>
-    <row r="60" spans="1:26">
+    <row r="60" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="3"/>
       <c r="B60" s="3"/>
       <c r="C60" s="3"/>
@@ -11726,56 +12389,47 @@
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A12:F14"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:Z60"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.796875" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="13.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="3" width="20" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="24" customWidth="1"/>
-    <col min="6" max="6" width="3" customWidth="1"/>
-    <col min="7" max="7" width="27" customWidth="1"/>
-    <col min="8" max="9" width="14" customWidth="1"/>
-    <col min="10" max="10" width="28" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="28"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="27.15" customHeight="1">
-      <c r="A1" s="29" t="s">
+    <row r="1" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="29" t="s">
-        <v>62</v>
-      </c>
-      <c r="C1" s="29" t="s">
-        <v>62</v>
-      </c>
-      <c r="D1" s="29" t="s">
-        <v>62</v>
-      </c>
-      <c r="E1" s="29" t="s">
-        <v>62</v>
-      </c>
-      <c r="F1" s="29" t="s">
-        <v>62</v>
-      </c>
-      <c r="G1" s="29" t="s">
-        <v>62</v>
-      </c>
-      <c r="H1" s="29" t="s">
-        <v>62</v>
-      </c>
-      <c r="I1" s="29" t="s">
-        <v>62</v>
-      </c>
-      <c r="J1" s="29" t="s">
-        <v>62</v>
-      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
       <c r="K1" s="3"/>
       <c r="L1" s="3"/>
       <c r="M1" s="3"/>
@@ -11793,7 +12447,7 @@
       <c r="Y1" s="3"/>
       <c r="Z1" s="3"/>
     </row>
-    <row r="2" spans="1:26">
+    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -11821,33 +12475,33 @@
       <c r="Y2" s="3"/>
       <c r="Z2" s="3"/>
     </row>
-    <row r="3" spans="1:26">
-      <c r="A3" s="2" t="s">
+    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="5" t="s">
         <v>67</v>
       </c>
       <c r="F3" s="3"/>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" s="5" t="s">
         <v>22</v>
       </c>
       <c r="K3" s="3"/>
@@ -11867,27 +12521,27 @@
       <c r="Y3" s="3"/>
       <c r="Z3" s="3"/>
     </row>
-    <row r="4" spans="1:26">
-      <c r="A4" s="4">
+    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="5"/>
+      <c r="B4" s="23"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="8"/>
       <c r="F4" s="3"/>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="H4" s="19" t="str">
-        <f>IF(COUNT($B$4:$B$33)=0,"",COUNT($B$4:$B$33))</f>
+      <c r="H4" s="23" t="str">
+        <f aca="false">IF(COUNT($B$4:$B$33)=0,"",COUNT($B$4:$B$33))</f>
         <v/>
       </c>
-      <c r="I4" s="19" t="str">
-        <f>IF(COUNT($C$4:$C$33)=0,"",COUNT($C$4:$C$33))</f>
+      <c r="I4" s="23" t="str">
+        <f aca="false">IF(COUNT($C$4:$C$33)=0,"",COUNT($C$4:$C$33))</f>
         <v/>
       </c>
-      <c r="J4" s="5" t="s">
+      <c r="J4" s="8" t="s">
         <v>70</v>
       </c>
       <c r="K4" s="3"/>
@@ -11907,27 +12561,27 @@
       <c r="Y4" s="3"/>
       <c r="Z4" s="3"/>
     </row>
-    <row r="5" spans="1:26">
-      <c r="A5" s="6">
+    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="7"/>
+      <c r="B5" s="24"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="10"/>
       <c r="F5" s="3"/>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="H5" s="1" t="str">
-        <f>IF(COUNT($B$4:$B$33)=0,"",_xludf.MODE.SNGL($B$4:$B$33))</f>
+      <c r="H5" s="24" t="str">
+        <f aca="false">IF(COUNT($B$4:$B$33)=0,"",_xludf.mode.sngl($B$4:$B$33))</f>
         <v/>
       </c>
-      <c r="I5" s="1" t="str">
-        <f>IF(COUNT($C$4:$C$33)=0,"",_xludf.MODE.SNGL($C$4:$C$33))</f>
+      <c r="I5" s="24" t="str">
+        <f aca="false">IF(COUNT($C$4:$C$33)=0,"",_xludf.mode.sngl($C$4:$C$33))</f>
         <v/>
       </c>
-      <c r="J5" s="7" t="s">
+      <c r="J5" s="10" t="s">
         <v>72</v>
       </c>
       <c r="K5" s="3"/>
@@ -11947,27 +12601,27 @@
       <c r="Y5" s="3"/>
       <c r="Z5" s="3"/>
     </row>
-    <row r="6" spans="1:26">
-      <c r="A6" s="6">
+    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="7"/>
+      <c r="B6" s="24"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="10"/>
       <c r="F6" s="3"/>
-      <c r="G6" s="6" t="s">
+      <c r="G6" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="H6" s="1" t="str">
-        <f>IF(COUNT($B$4:$B$33)=0,"",MEDIAN($B$4:$B$33))</f>
+      <c r="H6" s="24" t="str">
+        <f aca="false">IF(COUNT($B$4:$B$33)=0,"",MEDIAN($B$4:$B$33))</f>
         <v/>
       </c>
-      <c r="I6" s="1" t="str">
-        <f>IF(COUNT($C$4:$C$33)=0,"",MEDIAN($C$4:$C$33))</f>
+      <c r="I6" s="24" t="str">
+        <f aca="false">IF(COUNT($C$4:$C$33)=0,"",MEDIAN($C$4:$C$33))</f>
         <v/>
       </c>
-      <c r="J6" s="7" t="s">
+      <c r="J6" s="10" t="s">
         <v>73</v>
       </c>
       <c r="K6" s="3"/>
@@ -11987,27 +12641,27 @@
       <c r="Y6" s="3"/>
       <c r="Z6" s="3"/>
     </row>
-    <row r="7" spans="1:26">
-      <c r="A7" s="6">
+    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="7"/>
+      <c r="B7" s="24"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="24"/>
+      <c r="E7" s="10"/>
       <c r="F7" s="3"/>
-      <c r="G7" s="6" t="s">
+      <c r="G7" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H7" s="24" t="str">
-        <f>IF(COUNT($B$4:$B$33)=0,"",AVERAGE($B$4:$B$33))</f>
+      <c r="H7" s="30" t="str">
+        <f aca="false">IF(COUNT($B$4:$B$33)=0,"",AVERAGE($B$4:$B$33))</f>
         <v/>
       </c>
-      <c r="I7" s="24" t="str">
-        <f>IF(COUNT($C$4:$C$33)=0,"",AVERAGE($C$4:$C$33))</f>
+      <c r="I7" s="30" t="str">
+        <f aca="false">IF(COUNT($C$4:$C$33)=0,"",AVERAGE($C$4:$C$33))</f>
         <v/>
       </c>
-      <c r="J7" s="7" t="s">
+      <c r="J7" s="10" t="s">
         <v>74</v>
       </c>
       <c r="K7" s="3"/>
@@ -12027,27 +12681,27 @@
       <c r="Y7" s="3"/>
       <c r="Z7" s="3"/>
     </row>
-    <row r="8" spans="1:26">
-      <c r="A8" s="6">
+    <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="7"/>
+      <c r="B8" s="24"/>
+      <c r="C8" s="24"/>
+      <c r="D8" s="24"/>
+      <c r="E8" s="10"/>
       <c r="F8" s="3"/>
-      <c r="G8" s="6" t="s">
+      <c r="G8" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="H8" s="24" t="str">
-        <f>IF(COUNT($B$4:$B$33)=0,"",_xludf.VAR.S($B$4:$B$33))</f>
+      <c r="H8" s="30" t="str">
+        <f aca="false">IF(COUNT($B$4:$B$33)=0,"",_xludf.var.s($B$4:$B$33))</f>
         <v/>
       </c>
-      <c r="I8" s="24" t="str">
-        <f>IF(COUNT($C$4:$C$33)=0,"",_xludf.VAR.S($C$4:$C$33))</f>
+      <c r="I8" s="30" t="str">
+        <f aca="false">IF(COUNT($C$4:$C$33)=0,"",_xludf.var.s($C$4:$C$33))</f>
         <v/>
       </c>
-      <c r="J8" s="7" t="s">
+      <c r="J8" s="10" t="s">
         <v>76</v>
       </c>
       <c r="K8" s="3"/>
@@ -12067,27 +12721,27 @@
       <c r="Y8" s="3"/>
       <c r="Z8" s="3"/>
     </row>
-    <row r="9" spans="1:26">
-      <c r="A9" s="6">
+    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="7"/>
+      <c r="B9" s="24"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="24"/>
+      <c r="E9" s="10"/>
       <c r="F9" s="3"/>
-      <c r="G9" s="6" t="s">
+      <c r="G9" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="H9" s="24" t="str">
-        <f>IF(COUNT($B$4:$B$33)=0,"",_xludf.STDEV.S($B$4:$B$33))</f>
+      <c r="H9" s="30" t="str">
+        <f aca="false">IF(COUNT($B$4:$B$33)=0,"",_xludf.stdev.s($B$4:$B$33))</f>
         <v/>
       </c>
-      <c r="I9" s="24" t="str">
-        <f>IF(COUNT($C$4:$C$33)=0,"",_xludf.STDEV.S($C$4:$C$33))</f>
+      <c r="I9" s="30" t="str">
+        <f aca="false">IF(COUNT($C$4:$C$33)=0,"",_xludf.stdev.s($C$4:$C$33))</f>
         <v/>
       </c>
-      <c r="J9" s="7" t="s">
+      <c r="J9" s="10" t="s">
         <v>77</v>
       </c>
       <c r="K9" s="3"/>
@@ -12107,27 +12761,27 @@
       <c r="Y9" s="3"/>
       <c r="Z9" s="3"/>
     </row>
-    <row r="10" spans="1:26">
-      <c r="A10" s="6">
+    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="7"/>
+      <c r="B10" s="24"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="10"/>
       <c r="F10" s="3"/>
-      <c r="G10" s="8" t="s">
+      <c r="G10" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="H10" s="20" t="str">
-        <f>IF(COUNT($B$4:$B$33)=0,"",MAX($B$4:$B$33)-MIN($B$4:$B$33))</f>
+      <c r="H10" s="25" t="str">
+        <f aca="false">IF(COUNT($B$4:$B$33)=0,"",MAX($B$4:$B$33)-MIN($B$4:$B$33))</f>
         <v/>
       </c>
-      <c r="I10" s="20" t="str">
-        <f>IF(COUNT($C$4:$C$33)=0,"",MAX($C$4:$C$33)-MIN($C$4:$C$33))</f>
+      <c r="I10" s="25" t="str">
+        <f aca="false">IF(COUNT($C$4:$C$33)=0,"",MAX($C$4:$C$33)-MIN($C$4:$C$33))</f>
         <v/>
       </c>
-      <c r="J10" s="9" t="s">
+      <c r="J10" s="12" t="s">
         <v>79</v>
       </c>
       <c r="K10" s="3"/>
@@ -12147,14 +12801,14 @@
       <c r="Y10" s="3"/>
       <c r="Z10" s="3"/>
     </row>
-    <row r="11" spans="1:26">
-      <c r="A11" s="6">
+    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="7"/>
+      <c r="B11" s="24"/>
+      <c r="C11" s="24"/>
+      <c r="D11" s="24"/>
+      <c r="E11" s="10"/>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
@@ -12177,21 +12831,21 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
     </row>
-    <row r="12" spans="1:26">
-      <c r="A12" s="6">
+    <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="7"/>
+      <c r="B12" s="24"/>
+      <c r="C12" s="24"/>
+      <c r="D12" s="24"/>
+      <c r="E12" s="10"/>
       <c r="F12" s="3"/>
-      <c r="G12" s="31" t="s">
+      <c r="G12" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="H12" s="31"/>
-      <c r="I12" s="31"/>
-      <c r="J12" s="31"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="6"/>
+      <c r="J12" s="6"/>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
@@ -12209,19 +12863,19 @@
       <c r="Y12" s="3"/>
       <c r="Z12" s="3"/>
     </row>
-    <row r="13" spans="1:26">
-      <c r="A13" s="6">
+    <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="7"/>
+      <c r="B13" s="24"/>
+      <c r="C13" s="24"/>
+      <c r="D13" s="24"/>
+      <c r="E13" s="10"/>
       <c r="F13" s="3"/>
-      <c r="G13" s="31"/>
-      <c r="H13" s="31"/>
-      <c r="I13" s="31"/>
-      <c r="J13" s="31"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="6"/>
+      <c r="J13" s="6"/>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
       <c r="M13" s="3"/>
@@ -12239,19 +12893,19 @@
       <c r="Y13" s="3"/>
       <c r="Z13" s="3"/>
     </row>
-    <row r="14" spans="1:26">
-      <c r="A14" s="6">
+    <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="7"/>
+      <c r="B14" s="24"/>
+      <c r="C14" s="24"/>
+      <c r="D14" s="24"/>
+      <c r="E14" s="10"/>
       <c r="F14" s="3"/>
-      <c r="G14" s="31"/>
-      <c r="H14" s="31"/>
-      <c r="I14" s="31"/>
-      <c r="J14" s="31"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="6"/>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
@@ -12269,19 +12923,19 @@
       <c r="Y14" s="3"/>
       <c r="Z14" s="3"/>
     </row>
-    <row r="15" spans="1:26">
-      <c r="A15" s="6">
+    <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="7"/>
+      <c r="B15" s="24"/>
+      <c r="C15" s="24"/>
+      <c r="D15" s="24"/>
+      <c r="E15" s="10"/>
       <c r="F15" s="3"/>
-      <c r="G15" s="31"/>
-      <c r="H15" s="31"/>
-      <c r="I15" s="31"/>
-      <c r="J15" s="31"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="6"/>
+      <c r="J15" s="6"/>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
@@ -12299,19 +12953,19 @@
       <c r="Y15" s="3"/>
       <c r="Z15" s="3"/>
     </row>
-    <row r="16" spans="1:26">
-      <c r="A16" s="6">
+    <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="7"/>
+      <c r="B16" s="24"/>
+      <c r="C16" s="24"/>
+      <c r="D16" s="24"/>
+      <c r="E16" s="10"/>
       <c r="F16" s="3"/>
-      <c r="G16" s="31"/>
-      <c r="H16" s="31"/>
-      <c r="I16" s="31"/>
-      <c r="J16" s="31"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="6"/>
+      <c r="J16" s="6"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
@@ -12329,19 +12983,19 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
     </row>
-    <row r="17" spans="1:26">
-      <c r="A17" s="6">
+    <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="9" t="n">
         <v>14</v>
       </c>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="7"/>
+      <c r="B17" s="24"/>
+      <c r="C17" s="24"/>
+      <c r="D17" s="24"/>
+      <c r="E17" s="10"/>
       <c r="F17" s="3"/>
-      <c r="G17" s="31"/>
-      <c r="H17" s="31"/>
-      <c r="I17" s="31"/>
-      <c r="J17" s="31"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="6"/>
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
       <c r="M17" s="3"/>
@@ -12359,14 +13013,14 @@
       <c r="Y17" s="3"/>
       <c r="Z17" s="3"/>
     </row>
-    <row r="18" spans="1:26">
-      <c r="A18" s="6">
+    <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="7"/>
+      <c r="B18" s="24"/>
+      <c r="C18" s="24"/>
+      <c r="D18" s="24"/>
+      <c r="E18" s="10"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
@@ -12389,14 +13043,14 @@
       <c r="Y18" s="3"/>
       <c r="Z18" s="3"/>
     </row>
-    <row r="19" spans="1:26">
-      <c r="A19" s="6">
+    <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="7"/>
+      <c r="B19" s="24"/>
+      <c r="C19" s="24"/>
+      <c r="D19" s="24"/>
+      <c r="E19" s="10"/>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
@@ -12419,14 +13073,14 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
     </row>
-    <row r="20" spans="1:26">
-      <c r="A20" s="6">
+    <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="9" t="n">
         <v>17</v>
       </c>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="7"/>
+      <c r="B20" s="24"/>
+      <c r="C20" s="24"/>
+      <c r="D20" s="24"/>
+      <c r="E20" s="10"/>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
@@ -12449,14 +13103,14 @@
       <c r="Y20" s="3"/>
       <c r="Z20" s="3"/>
     </row>
-    <row r="21" spans="1:26">
-      <c r="A21" s="6">
+    <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="9" t="n">
         <v>18</v>
       </c>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="7"/>
+      <c r="B21" s="24"/>
+      <c r="C21" s="24"/>
+      <c r="D21" s="24"/>
+      <c r="E21" s="10"/>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
@@ -12479,14 +13133,14 @@
       <c r="Y21" s="3"/>
       <c r="Z21" s="3"/>
     </row>
-    <row r="22" spans="1:26">
-      <c r="A22" s="6">
+    <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="7"/>
+      <c r="B22" s="24"/>
+      <c r="C22" s="24"/>
+      <c r="D22" s="24"/>
+      <c r="E22" s="10"/>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
@@ -12509,14 +13163,14 @@
       <c r="Y22" s="3"/>
       <c r="Z22" s="3"/>
     </row>
-    <row r="23" spans="1:26">
-      <c r="A23" s="6">
+    <row r="23" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="7"/>
+      <c r="B23" s="24"/>
+      <c r="C23" s="24"/>
+      <c r="D23" s="24"/>
+      <c r="E23" s="10"/>
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
@@ -12539,14 +13193,14 @@
       <c r="Y23" s="3"/>
       <c r="Z23" s="3"/>
     </row>
-    <row r="24" spans="1:26">
-      <c r="A24" s="6">
+    <row r="24" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="7"/>
+      <c r="B24" s="24"/>
+      <c r="C24" s="24"/>
+      <c r="D24" s="24"/>
+      <c r="E24" s="10"/>
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
@@ -12569,14 +13223,14 @@
       <c r="Y24" s="3"/>
       <c r="Z24" s="3"/>
     </row>
-    <row r="25" spans="1:26">
-      <c r="A25" s="6">
+    <row r="25" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="7"/>
+      <c r="B25" s="24"/>
+      <c r="C25" s="24"/>
+      <c r="D25" s="24"/>
+      <c r="E25" s="10"/>
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
@@ -12599,14 +13253,14 @@
       <c r="Y25" s="3"/>
       <c r="Z25" s="3"/>
     </row>
-    <row r="26" spans="1:26">
-      <c r="A26" s="6">
+    <row r="26" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="9" t="n">
         <v>23</v>
       </c>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="7"/>
+      <c r="B26" s="24"/>
+      <c r="C26" s="24"/>
+      <c r="D26" s="24"/>
+      <c r="E26" s="10"/>
       <c r="F26" s="3"/>
       <c r="G26" s="3"/>
       <c r="H26" s="3"/>
@@ -12629,14 +13283,14 @@
       <c r="Y26" s="3"/>
       <c r="Z26" s="3"/>
     </row>
-    <row r="27" spans="1:26">
-      <c r="A27" s="6">
+    <row r="27" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="7"/>
+      <c r="B27" s="24"/>
+      <c r="C27" s="24"/>
+      <c r="D27" s="24"/>
+      <c r="E27" s="10"/>
       <c r="F27" s="3"/>
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
@@ -12659,14 +13313,14 @@
       <c r="Y27" s="3"/>
       <c r="Z27" s="3"/>
     </row>
-    <row r="28" spans="1:26">
-      <c r="A28" s="6">
+    <row r="28" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="B28" s="1"/>
-      <c r="C28" s="1"/>
-      <c r="D28" s="1"/>
-      <c r="E28" s="7"/>
+      <c r="B28" s="24"/>
+      <c r="C28" s="24"/>
+      <c r="D28" s="24"/>
+      <c r="E28" s="10"/>
       <c r="F28" s="3"/>
       <c r="G28" s="3"/>
       <c r="H28" s="3"/>
@@ -12689,14 +13343,14 @@
       <c r="Y28" s="3"/>
       <c r="Z28" s="3"/>
     </row>
-    <row r="29" spans="1:26">
-      <c r="A29" s="6">
+    <row r="29" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="B29" s="1"/>
-      <c r="C29" s="1"/>
-      <c r="D29" s="1"/>
-      <c r="E29" s="7"/>
+      <c r="B29" s="24"/>
+      <c r="C29" s="24"/>
+      <c r="D29" s="24"/>
+      <c r="E29" s="10"/>
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
@@ -12719,14 +13373,14 @@
       <c r="Y29" s="3"/>
       <c r="Z29" s="3"/>
     </row>
-    <row r="30" spans="1:26">
-      <c r="A30" s="6">
+    <row r="30" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="9" t="n">
         <v>27</v>
       </c>
-      <c r="B30" s="1"/>
-      <c r="C30" s="1"/>
-      <c r="D30" s="1"/>
-      <c r="E30" s="7"/>
+      <c r="B30" s="24"/>
+      <c r="C30" s="24"/>
+      <c r="D30" s="24"/>
+      <c r="E30" s="10"/>
       <c r="F30" s="3"/>
       <c r="G30" s="3"/>
       <c r="H30" s="3"/>
@@ -12749,14 +13403,14 @@
       <c r="Y30" s="3"/>
       <c r="Z30" s="3"/>
     </row>
-    <row r="31" spans="1:26">
-      <c r="A31" s="6">
+    <row r="31" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="9" t="n">
         <v>28</v>
       </c>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
-      <c r="E31" s="7"/>
+      <c r="B31" s="24"/>
+      <c r="C31" s="24"/>
+      <c r="D31" s="24"/>
+      <c r="E31" s="10"/>
       <c r="F31" s="3"/>
       <c r="G31" s="3"/>
       <c r="H31" s="3"/>
@@ -12779,14 +13433,14 @@
       <c r="Y31" s="3"/>
       <c r="Z31" s="3"/>
     </row>
-    <row r="32" spans="1:26">
-      <c r="A32" s="6">
+    <row r="32" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="9" t="n">
         <v>29</v>
       </c>
-      <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
-      <c r="D32" s="1"/>
-      <c r="E32" s="7"/>
+      <c r="B32" s="24"/>
+      <c r="C32" s="24"/>
+      <c r="D32" s="24"/>
+      <c r="E32" s="10"/>
       <c r="F32" s="3"/>
       <c r="G32" s="3"/>
       <c r="H32" s="3"/>
@@ -12809,14 +13463,14 @@
       <c r="Y32" s="3"/>
       <c r="Z32" s="3"/>
     </row>
-    <row r="33" spans="1:26">
-      <c r="A33" s="8">
+    <row r="33" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="B33" s="20"/>
-      <c r="C33" s="20"/>
-      <c r="D33" s="20"/>
-      <c r="E33" s="9"/>
+      <c r="B33" s="25"/>
+      <c r="C33" s="25"/>
+      <c r="D33" s="25"/>
+      <c r="E33" s="12"/>
       <c r="F33" s="3"/>
       <c r="G33" s="3"/>
       <c r="H33" s="3"/>
@@ -12839,7 +13493,7 @@
       <c r="Y33" s="3"/>
       <c r="Z33" s="3"/>
     </row>
-    <row r="34" spans="1:26">
+    <row r="34" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="3"/>
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
@@ -12867,7 +13521,7 @@
       <c r="Y34" s="3"/>
       <c r="Z34" s="3"/>
     </row>
-    <row r="35" spans="1:26">
+    <row r="35" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="3"/>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
@@ -12895,7 +13549,7 @@
       <c r="Y35" s="3"/>
       <c r="Z35" s="3"/>
     </row>
-    <row r="36" spans="1:26">
+    <row r="36" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="3"/>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
@@ -12923,7 +13577,7 @@
       <c r="Y36" s="3"/>
       <c r="Z36" s="3"/>
     </row>
-    <row r="37" spans="1:26">
+    <row r="37" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="3"/>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
@@ -12951,7 +13605,7 @@
       <c r="Y37" s="3"/>
       <c r="Z37" s="3"/>
     </row>
-    <row r="38" spans="1:26">
+    <row r="38" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="3"/>
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
@@ -12979,7 +13633,7 @@
       <c r="Y38" s="3"/>
       <c r="Z38" s="3"/>
     </row>
-    <row r="39" spans="1:26">
+    <row r="39" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="3"/>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
@@ -13007,7 +13661,7 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
     </row>
-    <row r="40" spans="1:26">
+    <row r="40" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="3"/>
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
@@ -13035,7 +13689,7 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
     </row>
-    <row r="41" spans="1:26">
+    <row r="41" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="3"/>
       <c r="B41" s="3"/>
       <c r="C41" s="3"/>
@@ -13063,7 +13717,7 @@
       <c r="Y41" s="3"/>
       <c r="Z41" s="3"/>
     </row>
-    <row r="42" spans="1:26">
+    <row r="42" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="3"/>
       <c r="B42" s="3"/>
       <c r="C42" s="3"/>
@@ -13091,7 +13745,7 @@
       <c r="Y42" s="3"/>
       <c r="Z42" s="3"/>
     </row>
-    <row r="43" spans="1:26">
+    <row r="43" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="3"/>
       <c r="B43" s="3"/>
       <c r="C43" s="3"/>
@@ -13119,7 +13773,7 @@
       <c r="Y43" s="3"/>
       <c r="Z43" s="3"/>
     </row>
-    <row r="44" spans="1:26">
+    <row r="44" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="3"/>
       <c r="B44" s="3"/>
       <c r="C44" s="3"/>
@@ -13147,7 +13801,7 @@
       <c r="Y44" s="3"/>
       <c r="Z44" s="3"/>
     </row>
-    <row r="45" spans="1:26">
+    <row r="45" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="3"/>
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
@@ -13175,7 +13829,7 @@
       <c r="Y45" s="3"/>
       <c r="Z45" s="3"/>
     </row>
-    <row r="46" spans="1:26">
+    <row r="46" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="3"/>
       <c r="B46" s="3"/>
       <c r="C46" s="3"/>
@@ -13203,7 +13857,7 @@
       <c r="Y46" s="3"/>
       <c r="Z46" s="3"/>
     </row>
-    <row r="47" spans="1:26">
+    <row r="47" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="3"/>
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
@@ -13231,7 +13885,7 @@
       <c r="Y47" s="3"/>
       <c r="Z47" s="3"/>
     </row>
-    <row r="48" spans="1:26">
+    <row r="48" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="3"/>
       <c r="B48" s="3"/>
       <c r="C48" s="3"/>
@@ -13259,7 +13913,7 @@
       <c r="Y48" s="3"/>
       <c r="Z48" s="3"/>
     </row>
-    <row r="49" spans="1:26">
+    <row r="49" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="3"/>
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
@@ -13287,7 +13941,7 @@
       <c r="Y49" s="3"/>
       <c r="Z49" s="3"/>
     </row>
-    <row r="50" spans="1:26">
+    <row r="50" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="3"/>
       <c r="B50" s="3"/>
       <c r="C50" s="3"/>
@@ -13315,7 +13969,7 @@
       <c r="Y50" s="3"/>
       <c r="Z50" s="3"/>
     </row>
-    <row r="51" spans="1:26">
+    <row r="51" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="3"/>
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
@@ -13343,7 +13997,7 @@
       <c r="Y51" s="3"/>
       <c r="Z51" s="3"/>
     </row>
-    <row r="52" spans="1:26">
+    <row r="52" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="3"/>
       <c r="B52" s="3"/>
       <c r="C52" s="3"/>
@@ -13371,7 +14025,7 @@
       <c r="Y52" s="3"/>
       <c r="Z52" s="3"/>
     </row>
-    <row r="53" spans="1:26">
+    <row r="53" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="3"/>
       <c r="B53" s="3"/>
       <c r="C53" s="3"/>
@@ -13399,7 +14053,7 @@
       <c r="Y53" s="3"/>
       <c r="Z53" s="3"/>
     </row>
-    <row r="54" spans="1:26">
+    <row r="54" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="3"/>
       <c r="B54" s="3"/>
       <c r="C54" s="3"/>
@@ -13427,7 +14081,7 @@
       <c r="Y54" s="3"/>
       <c r="Z54" s="3"/>
     </row>
-    <row r="55" spans="1:26">
+    <row r="55" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="3"/>
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
@@ -13455,7 +14109,7 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
     </row>
-    <row r="56" spans="1:26">
+    <row r="56" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="3"/>
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
@@ -13483,7 +14137,7 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
     </row>
-    <row r="57" spans="1:26">
+    <row r="57" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="3"/>
       <c r="B57" s="3"/>
       <c r="C57" s="3"/>
@@ -13511,7 +14165,7 @@
       <c r="Y57" s="3"/>
       <c r="Z57" s="3"/>
     </row>
-    <row r="58" spans="1:26">
+    <row r="58" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="3"/>
       <c r="B58" s="3"/>
       <c r="C58" s="3"/>
@@ -13539,7 +14193,7 @@
       <c r="Y58" s="3"/>
       <c r="Z58" s="3"/>
     </row>
-    <row r="59" spans="1:26">
+    <row r="59" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="3"/>
       <c r="B59" s="3"/>
       <c r="C59" s="3"/>
@@ -13567,7 +14221,7 @@
       <c r="Y59" s="3"/>
       <c r="Z59" s="3"/>
     </row>
-    <row r="60" spans="1:26">
+    <row r="60" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="3"/>
       <c r="B60" s="3"/>
       <c r="C60" s="3"/>
@@ -13600,6 +14254,12 @@
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="G12:J17"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>